--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3117998994965</v>
+        <v>139.310864738588</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4831133818291</v>
+        <v>142.4817446604747</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7630231414677</v>
+        <v>143.7615390504174</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.441607538326</v>
+        <v>144.4400814641709</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.368162161952</v>
+        <v>144.3666102107799</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2899878465177</v>
+        <v>144.2884141439078</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2464637086525</v>
+        <v>144.2448813937685</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2858649226454</v>
+        <v>144.2842854465578</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.955962566526</v>
+        <v>144.954377256178</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0368012691998</v>
+        <v>148.0368258987964</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315315353603</v>
+        <v>148.4315369050999</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535404436053</v>
+        <v>148.85354074759</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.921886564373</v>
+        <v>148.9220681524788</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2942454153959</v>
+        <v>149.2943031486434</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4076505188337</v>
+        <v>150.4074052887835</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8614076294411</v>
+        <v>151.8607582270635</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2503868539122</v>
+        <v>152.2496953676761</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5802590693829</v>
+        <v>152.5795891174955</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1794215029233</v>
+        <v>153.1789939220936</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4091610813192</v>
+        <v>152.4090554821886</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9106216524646</v>
+        <v>152.909601358834</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6934100549414</v>
+        <v>152.6920024137807</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7148258589883</v>
+        <v>152.7129758100488</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4037824734699</v>
+        <v>154.4015335326298</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.361024988106</v>
+        <v>155.358780369486</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3507073888223</v>
+        <v>156.3482480630055</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.006913266544</v>
+        <v>158.0042058111301</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6211267886098</v>
+        <v>159.618835241123</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4585809401217</v>
+        <v>161.4570700084335</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9025756422714</v>
+        <v>159.903382274031</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6228557032165</v>
+        <v>159.6232413212324</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2067898915569</v>
+        <v>159.2093462335975</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4554649292807</v>
+        <v>157.4587986329042</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9833425620836</v>
+        <v>157.9865481237036</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.2971212203221</v>
+        <v>158.3000842616821</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3450174922935</v>
+        <v>158.3480286186111</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5838025606872</v>
+        <v>159.5866524350717</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4296644656924</v>
+        <v>158.4309289007662</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7215218915835</v>
+        <v>155.7204808149251</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8657964951532</v>
+        <v>155.864685749102</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6634249313409</v>
+        <v>156.6629945756358</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3135885984155</v>
+        <v>156.3107706501935</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0806041400619</v>
+        <v>156.0776172144678</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9155654610686</v>
+        <v>155.9122878059701</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1703992172474</v>
+        <v>157.1684458366099</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6569483708846</v>
+        <v>158.657465626344</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1515381813607</v>
+        <v>159.152364696708</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7432732210403</v>
+        <v>159.7443982817348</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6064264171384</v>
+        <v>159.6066395698108</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1798359927135</v>
+        <v>160.1801849945575</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0544054879011</v>
+        <v>160.0536617113139</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8379959394875</v>
+        <v>159.8365504145538</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3179434779141</v>
+        <v>160.316717294664</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.030178274569</v>
+        <v>161.0283457488278</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6949776055926</v>
+        <v>161.6923761843028</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5461510564538</v>
+        <v>161.5443029408653</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5051789435512</v>
+        <v>160.5060442236528</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.066071863209</v>
+        <v>160.0678120895561</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.880923935873</v>
+        <v>159.8833198576534</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8962351130589</v>
+        <v>159.8990471949014</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6638993241156</v>
+        <v>159.5572818896181</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.757120031983</v>
+        <v>159.6307301037714</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.157490146395</v>
+        <v>160.0088586632208</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.5155692369383</v>
+        <v>160.3429066358934</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.8574002538374</v>
+        <v>160.6700471913565</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>161.1335171540884</v>
+        <v>160.9338336037574</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.2822495226349</v>
+        <v>161.0705058805646</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>161.1105894658347</v>
+        <v>160.8837046960049</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.9566929027705</v>
+        <v>160.7028509130362</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>160.7683025178881</v>
+        <v>160.4887060022073</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>161.6067870334289</v>
+        <v>161.2401573932342</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>162.8980095715825</v>
+        <v>162.3615523421318</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>165.8589200118303</v>
+        <v>164.8665115556877</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>161.5765982726582</v>
+        <v>160.473980665019</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.310864738588</v>
+        <v>139.3099492630728</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4817446604747</v>
+        <v>142.4804046608321</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7615390504174</v>
+        <v>143.7600859626067</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4400814641709</v>
+        <v>144.4385871272416</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3666102107799</v>
+        <v>144.3650905442531</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2884141439078</v>
+        <v>144.2868731872035</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2448813937685</v>
+        <v>144.2433320083747</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2842854465578</v>
+        <v>144.2827388414032</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.954377256178</v>
+        <v>144.9528247883443</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0368258987964</v>
+        <v>148.0368500018507</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315369050999</v>
+        <v>148.4315421564421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.85354074759</v>
+        <v>148.8535410403186</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9220681524788</v>
+        <v>148.9222458656078</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2943031486434</v>
+        <v>149.2943597298669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4074052887835</v>
+        <v>150.4071652665901</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8607582270635</v>
+        <v>151.8601223627632</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2496953676761</v>
+        <v>152.249018260817</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5795891174955</v>
+        <v>152.5789330095334</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1789939220936</v>
+        <v>153.1785751564172</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4090554821886</v>
+        <v>152.4089521186414</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.909601358834</v>
+        <v>152.9086028283006</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6920024137807</v>
+        <v>152.6906246352361</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7129758100488</v>
+        <v>152.7111646154357</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.4015335326298</v>
+        <v>154.3993316675337</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.358780369486</v>
+        <v>155.3565824147518</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3482480630055</v>
+        <v>156.3458396246505</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0042058111301</v>
+        <v>158.0015539661347</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.618835241123</v>
+        <v>159.6165897604177</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4570700084335</v>
+        <v>161.4555887667775</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.903382274031</v>
+        <v>159.9041699049238</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6232413212324</v>
+        <v>159.6236171333012</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2093462335975</v>
+        <v>159.211847490726</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4587986329042</v>
+        <v>157.4620613215603</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9865481237036</v>
+        <v>157.9896860579842</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3000842616821</v>
+        <v>158.302985578307</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3480286186111</v>
+        <v>158.3509793223659</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5866524350717</v>
+        <v>159.5894458388101</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4309289007662</v>
+        <v>158.4321697808001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7204808149251</v>
+        <v>155.7194627300421</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.864685749102</v>
+        <v>155.8635995825338</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6629945756358</v>
+        <v>156.6625748479241</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3107706501935</v>
+        <v>156.3080109448094</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0776172144678</v>
+        <v>156.0746914685459</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9122878059701</v>
+        <v>155.9090759318504</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1684458366099</v>
+        <v>157.1665312725202</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.657465626344</v>
+        <v>158.6579727732274</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.152364696708</v>
+        <v>159.1531752173339</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7443982817348</v>
+        <v>159.7455016841335</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6066395698108</v>
+        <v>159.6068493687589</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1801849945575</v>
+        <v>160.1805284798777</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0536617113139</v>
+        <v>160.0529344068886</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8365504145538</v>
+        <v>159.8351350703385</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.316717294664</v>
+        <v>160.3155167684909</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0283457488278</v>
+        <v>161.026550865562</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6923761843028</v>
+        <v>161.6898280171307</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5443029408653</v>
+        <v>161.5424896568114</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5060442236528</v>
+        <v>160.5068839658202</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0678120895561</v>
+        <v>160.069510985521</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8833198576534</v>
+        <v>159.8856633296321</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.8990471949014</v>
+        <v>159.9018038214314</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5572818896181</v>
+        <v>159.5625197693765</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.6307301037714</v>
+        <v>159.4742751213302</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>160.0088586632208</v>
+        <v>159.8221106096327</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.3429066358934</v>
+        <v>160.1372885935265</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.6700471913565</v>
+        <v>160.4499330519036</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>160.9338336037574</v>
+        <v>160.6915812753116</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>161.0705058805646</v>
+        <v>160.8112282874468</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.8837046960049</v>
+        <v>160.5997907928335</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.7028509130362</v>
+        <v>160.3811940862081</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>160.4887060022073</v>
+        <v>160.1350570733201</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>161.2401573932342</v>
+        <v>160.7986243602417</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>162.3615523421318</v>
+        <v>161.7457951688629</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>164.8665115556877</v>
+        <v>163.7098122164219</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>160.473980665019</v>
+        <v>159.1101188892528</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>157.3648688892528</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3099492630728</v>
+        <v>139.3090528578729</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4804046608321</v>
+        <v>142.4790924883029</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7600859626067</v>
+        <v>143.758662916736</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4385871272416</v>
+        <v>144.4371235479666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3650905442531</v>
+        <v>144.3636021656146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2868731872035</v>
+        <v>144.2853639651322</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2433320083747</v>
+        <v>144.2418145353919</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2827388414032</v>
+        <v>144.2812240918945</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9528247883443</v>
+        <v>144.9513041533292</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0368500018507</v>
+        <v>148.0368735950595</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315421564421</v>
+        <v>148.4315472932481</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535410403186</v>
+        <v>148.853541322289</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9222458656078</v>
+        <v>148.9224198264342</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2943597298669</v>
+        <v>149.2944151930412</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4071652665901</v>
+        <v>150.4069302882121</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8601223627632</v>
+        <v>151.8594996177917</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.249018260817</v>
+        <v>152.2483550896897</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5789330095334</v>
+        <v>152.5782903211442</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1785751564172</v>
+        <v>153.1781649362636</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4089521186414</v>
+        <v>152.4088509204238</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9086028283006</v>
+        <v>152.9076253724579</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6906246352361</v>
+        <v>152.6892757799875</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7111646154357</v>
+        <v>152.7093910650086</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3993316675337</v>
+        <v>154.3971754170137</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3565824147518</v>
+        <v>155.3544296859459</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3458396246505</v>
+        <v>156.3434805135592</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.0015539661347</v>
+        <v>157.9989560399594</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6165897604177</v>
+        <v>159.6143889776058</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4555887667775</v>
+        <v>161.4541363538589</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9041699049238</v>
+        <v>159.904939190068</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6236171333012</v>
+        <v>159.6239834974141</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.211847490726</v>
+        <v>159.2142954206541</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4620613215603</v>
+        <v>157.4652552361838</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9896860579842</v>
+        <v>157.9927584776555</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.302985578307</v>
+        <v>158.3058270730959</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3509793223659</v>
+        <v>158.3538713972296</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5894458388101</v>
+        <v>159.5921844251399</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4321697808001</v>
+        <v>158.4333877465469</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7194627300421</v>
+        <v>155.718466886231</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8635995825338</v>
+        <v>155.8625371918082</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6625748479241</v>
+        <v>156.6621653690586</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3080109448094</v>
+        <v>156.3053076985117</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0746914685459</v>
+        <v>156.0718250465279</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9090759318504</v>
+        <v>155.9059278845519</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1665312725202</v>
+        <v>157.1646543834419</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6579727732274</v>
+        <v>158.65847010305</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1531752173339</v>
+        <v>159.1539701995948</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7455016841335</v>
+        <v>159.7465840420888</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6068493687589</v>
+        <v>159.607055883902</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1805284798777</v>
+        <v>160.1808665655425</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0529344068886</v>
+        <v>160.0522230367875</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8351350703385</v>
+        <v>159.833748973278</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3155167684909</v>
+        <v>160.3143411046095</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.026550865562</v>
+        <v>161.0247924814009</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6898280171307</v>
+        <v>161.687331493813</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5424896568114</v>
+        <v>161.5407102501837</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5068839658202</v>
+        <v>160.5076991840459</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.069510985521</v>
+        <v>160.0711699574986</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8856633296321</v>
+        <v>159.8879560096989</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9018038214314</v>
+        <v>159.9045065615339</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5625197693765</v>
+        <v>159.567654097018</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.4742751213302</v>
+        <v>159.2966850806015</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.8221106096327</v>
+        <v>159.6090318114026</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>160.1372885935265</v>
+        <v>159.9017194404398</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.4499330519036</v>
+        <v>160.1928442006779</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>160.6915812753116</v>
+        <v>160.4078078149444</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.8112282874468</v>
+        <v>160.5053212542651</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.5997907928335</v>
+        <v>160.2611676691419</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>160.3811940862081</v>
+        <v>159.9952408567351</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>160.1350570733201</v>
+        <v>159.7068622205736</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.7986243602417</v>
+        <v>160.2606014675229</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.7457951688629</v>
+        <v>161.0193727919909</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>163.7098122164219</v>
+        <v>162.5056484477148</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>159.1101188892528</v>
+        <v>157.7117732786902</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.3648688892528</v>
+        <v>155.9665232786902</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3090528578729</v>
+        <v>139.3081749332695</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4790924883029</v>
+        <v>142.4778072850558</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.758662916736</v>
+        <v>143.7572689908345</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4371235479666</v>
+        <v>144.4356897866652</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3636021656146</v>
+        <v>144.3621441187094</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2853639651322</v>
+        <v>144.2838855076265</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2418145353919</v>
+        <v>144.2403279991883</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2812240918945</v>
+        <v>144.2797402241194</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9513041533292</v>
+        <v>144.9498143823891</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0368735950595</v>
+        <v>148.0368966944212</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315472932481</v>
+        <v>148.4315523192138</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853541322289</v>
+        <v>148.8535415939731</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9224198264342</v>
+        <v>148.9225901525099</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2944151930412</v>
+        <v>149.2944695708254</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4069302882121</v>
+        <v>150.4067001964216</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8594996177917</v>
+        <v>151.8588895904849</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2483550896897</v>
+        <v>152.2477054287029</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5782903211442</v>
+        <v>152.5776606451284</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1781649362636</v>
+        <v>153.1777630028795</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4088509204238</v>
+        <v>152.4087518201955</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9076253724579</v>
+        <v>152.9066683316083</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6892757799875</v>
+        <v>152.6879549476613</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7093910650086</v>
+        <v>152.7076539983182</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3971754170137</v>
+        <v>154.395063379687</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3544296859459</v>
+        <v>155.3523208035008</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3434805135592</v>
+        <v>156.3411692325443</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9989560399594</v>
+        <v>157.9964104087481</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6143889776058</v>
+        <v>159.6122315772331</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4541363538589</v>
+        <v>161.45271194115</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.904939190068</v>
+        <v>159.9056907551128</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6239834974141</v>
+        <v>159.624340754726</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2142954206541</v>
+        <v>159.216691707248</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4652552361838</v>
+        <v>157.4683825245775</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9927584776555</v>
+        <v>157.9957674085532</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3058270730959</v>
+        <v>158.3086105717682</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3538713972296</v>
+        <v>158.3567065668676</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5921844251399</v>
+        <v>159.5948697837593</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4333877465469</v>
+        <v>158.4345834162411</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.718466886231</v>
+        <v>155.717492565015</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8625371918082</v>
+        <v>155.8614978078125</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6621653690586</v>
+        <v>156.6617657773831</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3053076985117</v>
+        <v>156.3026591995111</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0718250465279</v>
+        <v>156.0690161667508</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9059278845519</v>
+        <v>155.9028417862932</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1646543834419</v>
+        <v>157.1628140719962</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.65847010305</v>
+        <v>158.6589578963078</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1539701995948</v>
+        <v>159.1547500827993</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7465840420888</v>
+        <v>159.7476459467142</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.607055883902</v>
+        <v>159.6072591836883</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1808665655425</v>
+        <v>160.1811993658166</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0522230367875</v>
+        <v>160.0515270862076</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.833748973278</v>
+        <v>159.8323912278435</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3143411046095</v>
+        <v>160.3131895406394</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0247924814009</v>
+        <v>161.0230694986252</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.687331493813</v>
+        <v>161.6848850680173</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5407102501837</v>
+        <v>161.5389638004446</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5076991840459</v>
+        <v>160.5084908422265</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0711699574986</v>
+        <v>160.0727903504974</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8879560096989</v>
+        <v>159.890199488335</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9045065615339</v>
+        <v>159.9071569278054</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.567654097018</v>
+        <v>159.5726878422129</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.2966850806015</v>
+        <v>159.1540722827645</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.6090318114026</v>
+        <v>159.4388969820517</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.9017194404398</v>
+        <v>159.713912832288</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>160.1928442006779</v>
+        <v>159.9926138831166</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>160.4078078149444</v>
+        <v>160.185922477359</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.5053212542651</v>
+        <v>160.2678597474305</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.2611676691419</v>
+        <v>160.0028845813515</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.9952408567351</v>
+        <v>159.7058875133009</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.7068622205736</v>
+        <v>159.3918435167695</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.2606014675229</v>
+        <v>159.8760406878099</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.0193727919909</v>
+        <v>160.5063326202056</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>162.5056484477148</v>
+        <v>161.6349137214876</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.7117732786902</v>
+        <v>156.8804037988008</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>155.9665232786902</v>
+        <v>148.8523095182114</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3081749332695</v>
+        <v>139.30731492361</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4778072850558</v>
+        <v>142.4765482281579</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7572689908345</v>
+        <v>143.7559033002696</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4356897866652</v>
+        <v>144.434284941538</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3621441187094</v>
+        <v>144.3607154859396</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2838855076265</v>
+        <v>144.2824368837472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2403279991883</v>
+        <v>144.2388714634899</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2797402241194</v>
+        <v>144.2782863034551</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9498143823891</v>
+        <v>144.9483545456773</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0368966944212</v>
+        <v>148.0369193152721</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315523192138</v>
+        <v>148.4315572378778</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535415939731</v>
+        <v>148.8535418558178</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9225901525099</v>
+        <v>148.9227569565296</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2944695708254</v>
+        <v>149.2945228946255</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4067001964216</v>
+        <v>150.4064748404539</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8588895904849</v>
+        <v>151.858291895401</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2477054287029</v>
+        <v>152.2470688694104</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5776606451284</v>
+        <v>152.5770435905822</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1777630028795</v>
+        <v>153.1773691078466</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4087518201955</v>
+        <v>152.4086547533797</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9066683316083</v>
+        <v>152.9057310732826</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6879549476613</v>
+        <v>152.6866612748338</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7076539983182</v>
+        <v>152.7059523020839</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.395063379687</v>
+        <v>154.3929942109325</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3523208035008</v>
+        <v>155.3502544433092</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3411692325443</v>
+        <v>156.3389043442863</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9964104087481</v>
+        <v>157.9939155130378</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6122315772331</v>
+        <v>159.6101162947119</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.45271194115</v>
+        <v>161.4513147313594</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9056907551128</v>
+        <v>159.9064251978632</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.624340754726</v>
+        <v>159.624689230517</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.216691707248</v>
+        <v>159.2190379643581</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4683825245775</v>
+        <v>157.4714452461918</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9957674085532</v>
+        <v>157.9987147940294</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3086105717682</v>
+        <v>158.3113378267244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3567065668676</v>
+        <v>158.3594864883059</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5948697837593</v>
+        <v>159.5975034438314</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4345834162411</v>
+        <v>158.4357573865504</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.717492565015</v>
+        <v>155.7165390784382</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8614978078125</v>
+        <v>155.8604806941333</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6617657773831</v>
+        <v>156.6613757277494</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.3026591995111</v>
+        <v>156.300063804395</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0690161667508</v>
+        <v>156.0662631180041</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.9028417862932</v>
+        <v>155.8998158319872</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1628140719962</v>
+        <v>157.1610092828562</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6589578963078</v>
+        <v>158.6594364229885</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1547500827993</v>
+        <v>159.1555152899887</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7476459467142</v>
+        <v>159.7486879674138</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6072591836883</v>
+        <v>159.6074593350993</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1811993658166</v>
+        <v>160.1815269923849</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0515270862076</v>
+        <v>160.0508460621666</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8323912278435</v>
+        <v>159.8310609746264</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3131895406394</v>
+        <v>160.3120613449738</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0230694986252</v>
+        <v>161.0213808629209</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6848850680173</v>
+        <v>161.6824872542173</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5389638004446</v>
+        <v>161.5372494192182</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5084908422265</v>
+        <v>160.5092598571057</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0727903504974</v>
+        <v>160.0743734513751</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.890199488335</v>
+        <v>159.8923952919209</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9071569278054</v>
+        <v>159.9097563789297</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5726878422129</v>
+        <v>159.5776238648764</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.1540722827645</v>
+        <v>159.0126408312409</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.4388969820517</v>
+        <v>159.2705288990086</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.713912832288</v>
+        <v>159.5281861439928</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.9926138831166</v>
+        <v>159.7969829467607</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>160.185922477359</v>
+        <v>159.9693471198223</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.2678597474305</v>
+        <v>160.0374756901431</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>160.0028845813515</v>
+        <v>159.7544492624505</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.7058875133009</v>
+        <v>159.4306928182276</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.3918435167695</v>
+        <v>159.0954767439428</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.8760406878099</v>
+        <v>159.523148739555</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>160.5063326202056</v>
+        <v>159.9803880824112</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.6349137214876</v>
+        <v>160.8689224490714</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.8804037988008</v>
+        <v>156.2018464054036</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>148.8523095182114</v>
+        <v>149.0678909271348</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.30731492361</v>
+        <v>139.3064722860921</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4765482281579</v>
+        <v>142.4753145278173</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7559033002696</v>
+        <v>143.754564995876</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.434284941538</v>
+        <v>144.4329081467775</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3607154859396</v>
+        <v>144.3593153863399</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2824368837472</v>
+        <v>144.2810171997305</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2388714634899</v>
+        <v>144.2374440294166</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2782863034551</v>
+        <v>144.276861432607</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9483545456773</v>
+        <v>144.9469237503121</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0369193152721</v>
+        <v>148.0369414723206</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315572378778</v>
+        <v>148.4315620526305</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535418558178</v>
+        <v>148.8535421082469</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9227569565296</v>
+        <v>148.9229203465782</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2945228946255</v>
+        <v>149.2945751946535</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4064748404539</v>
+        <v>150.4062540756799</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.858291895401</v>
+        <v>151.8577061625104</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2470688694104</v>
+        <v>152.246445019657</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5770435905822</v>
+        <v>152.5764387820914</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1773691078466</v>
+        <v>153.1769830125708</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4086547533797</v>
+        <v>152.4085596580233</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9057310732826</v>
+        <v>152.9048129908508</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6866612748338</v>
+        <v>152.6853939331576</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7059523020839</v>
+        <v>152.7042849078235</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3929942109325</v>
+        <v>154.3909666200483</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3502544433092</v>
+        <v>155.3482293339691</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3389043442863</v>
+        <v>156.3366844683767</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9939155130378</v>
+        <v>157.9914698546072</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6101162947119</v>
+        <v>159.6080419138985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4513147313594</v>
+        <v>161.4499439569847</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9064251978632</v>
+        <v>159.9071430897988</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.624689230517</v>
+        <v>159.6250292350904</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2190379643581</v>
+        <v>159.2213357394143</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4714452461918</v>
+        <v>157.4744453766136</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.9987147940294</v>
+        <v>158.0016024990996</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3113378267244</v>
+        <v>158.3140105206788</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3594864883059</v>
+        <v>158.3622127551068</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.5975034438314</v>
+        <v>159.6000868768205</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4357573865504</v>
+        <v>158.4369102334815</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7165390784382</v>
+        <v>155.7156057674665</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8604806941333</v>
+        <v>155.8594851453426</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6613757277494</v>
+        <v>156.6609948905994</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.300063804395</v>
+        <v>156.2975199347532</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0662631180041</v>
+        <v>156.0635642560908</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8998158319872</v>
+        <v>155.8968482857698</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1610092828562</v>
+        <v>157.1592390007591</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6594364229885</v>
+        <v>158.6599059430553</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1555152899887</v>
+        <v>159.1562662286761</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7486879674138</v>
+        <v>159.7497106528583</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6074593350993</v>
+        <v>159.6076564036586</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1815269923849</v>
+        <v>160.181849554381</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0508460621666</v>
+        <v>160.0501794923644</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8310609746264</v>
+        <v>159.8297573885394</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3120613449738</v>
+        <v>160.3109558152466</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0213808629209</v>
+        <v>161.0197255612637</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6824872542173</v>
+        <v>161.6801366247495</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5372494192182</v>
+        <v>161.5355662489476</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5092598571057</v>
+        <v>160.5100071010174</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0743734513751</v>
+        <v>160.0759204918772</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8923952919209</v>
+        <v>159.8945448858558</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9097563789297</v>
+        <v>159.9123063219423</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5776238648764</v>
+        <v>159.582464920062</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.0126408312409</v>
+        <v>158.8775775604151</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.2705288990086</v>
+        <v>159.1149633745157</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.5281861439928</v>
+        <v>159.3590715045413</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.7969829467607</v>
+        <v>159.6201401095294</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.9693471198223</v>
+        <v>159.7831746406858</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>160.0374756901431</v>
+        <v>159.840155027889</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.7544492624505</v>
+        <v>159.5456608366886</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.4306928182276</v>
+        <v>159.2049258174922</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.0954767439428</v>
+        <v>158.8238174755109</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.523148739555</v>
+        <v>159.1878203962146</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.9803880824112</v>
+        <v>159.5465233539722</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>160.8689224490714</v>
+        <v>160.2473630606203</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.2018464054036</v>
+        <v>155.7183395059948</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>149.0678909271348</v>
+        <v>149.3818650348973</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3064722860921</v>
+        <v>139.3056464996222</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4753145278173</v>
+        <v>142.4741054257319</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.754564995876</v>
+        <v>143.7532532621963</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4329081467775</v>
+        <v>144.4315585707906</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3593153863399</v>
+        <v>144.3579429737686</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2810171997305</v>
+        <v>144.2796255971517</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2374440294166</v>
+        <v>144.2360448336337</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.276861432607</v>
+        <v>144.275464749764</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9469237503121</v>
+        <v>144.9455211385589</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0369414723206</v>
+        <v>148.0369631796784</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315620526305</v>
+        <v>148.431566766721</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535421082469</v>
+        <v>148.8535423516624</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9229203465782</v>
+        <v>148.9230804263648</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2945751946535</v>
+        <v>149.2946264999835</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4062540756799</v>
+        <v>150.4060377632962</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8577061625104</v>
+        <v>151.8571320364328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.246445019657</v>
+        <v>152.2458335027746</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5764387820914</v>
+        <v>152.5758458589717</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1769830125708</v>
+        <v>153.176604487802</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4085596580233</v>
+        <v>152.4084664746647</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9048129908508</v>
+        <v>152.9039135022168</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6853939331576</v>
+        <v>152.6841521275993</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7042849078235</v>
+        <v>152.7026507896244</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3909666200483</v>
+        <v>154.3889793675791</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3482293339691</v>
+        <v>155.3462442541914</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3366844683767</v>
+        <v>156.3345082785338</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9914698546072</v>
+        <v>157.9890719935068</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6080419138985</v>
+        <v>159.6060072648074</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4499439569847</v>
+        <v>161.448598878944</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9071430897988</v>
+        <v>159.9078449774957</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6250292350904</v>
+        <v>159.6253610646109</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2213357394143</v>
+        <v>159.2235865168022</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4744453766136</v>
+        <v>157.4773848117848</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0016024990996</v>
+        <v>158.0044323143417</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3140105206788</v>
+        <v>158.3166302700789</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3622127551068</v>
+        <v>158.3648869003654</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6000868768205</v>
+        <v>159.6026214991719</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4369102334815</v>
+        <v>158.4380425132422</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7156057674665</v>
+        <v>155.7146920004883</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8594851453426</v>
+        <v>155.8585104853907</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6609948905994</v>
+        <v>156.6606229511071</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2975199347532</v>
+        <v>156.295026074002</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0635642560908</v>
+        <v>156.0609180005878</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8968482857698</v>
+        <v>155.8939374777253</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1592390007591</v>
+        <v>157.1575022486307</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6599059430553</v>
+        <v>158.6603667069041</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1562662286761</v>
+        <v>159.1570032915449</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7497106528583</v>
+        <v>159.7507145319093</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6076564036586</v>
+        <v>159.6078504534428</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.181849554381</v>
+        <v>160.18216715842</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0501794923644</v>
+        <v>160.0495269241151</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8297573885394</v>
+        <v>159.8284796771234</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3109558152466</v>
+        <v>160.3098722768896</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0197255612637</v>
+        <v>161.0181026199253</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6801366247495</v>
+        <v>161.6778318070373</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5355662489476</v>
+        <v>161.5339134616159</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5100071010174</v>
+        <v>160.5107334044446</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0759204918772</v>
+        <v>160.0774326514899</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8945448858558</v>
+        <v>159.8966496775015</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9123063219423</v>
+        <v>159.9148081143892</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.582464920062</v>
+        <v>159.5872136626039</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8775775604151</v>
+        <v>158.7347302803485</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.1149633745157</v>
+        <v>158.9490147399369</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.3590715045413</v>
+        <v>159.1775367007586</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.6201401095294</v>
+        <v>159.4284047603003</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.7831746406858</v>
+        <v>159.5814940968073</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.840155027889</v>
+        <v>159.6267433642342</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.5456608366886</v>
+        <v>159.3191415917526</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.2049258174922</v>
+        <v>158.9594914573972</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.8238174755109</v>
+        <v>158.5363049715417</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.1878203962146</v>
+        <v>158.8377077919071</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.5465233539722</v>
+        <v>159.1021880267496</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>160.2473630606203</v>
+        <v>159.6318189592514</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.7183395059948</v>
+        <v>155.2211243092382</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>149.3818650348973</v>
+        <v>149.4011636354959</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3056464996222</v>
+        <v>139.3048370637405</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4741054257319</v>
+        <v>142.4729201935356</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7532532621963</v>
+        <v>143.7519673158247</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4315585707906</v>
+        <v>144.4302354145257</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3579429737686</v>
+        <v>144.356597435204</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2796255971517</v>
+        <v>144.2782612511954</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2360448336337</v>
+        <v>144.2346730466131</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.275464749764</v>
+        <v>144.2740954268625</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9455211385589</v>
+        <v>144.9441458861182</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0369631796784</v>
+        <v>148.036984450891</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.431566766721</v>
+        <v>148.4315713832647</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535423516624</v>
+        <v>148.8535425864457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9230804263648</v>
+        <v>148.9232372954413</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2946264999835</v>
+        <v>149.2946768386045</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4060377632962</v>
+        <v>150.4058257700355</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8571320364328</v>
+        <v>151.8565691757204</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2458335027746</v>
+        <v>152.2452339568258</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5758458589717</v>
+        <v>152.5752644745544</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.176604487802</v>
+        <v>153.1762333131809</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4084664746647</v>
+        <v>152.40837514621</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9039135022168</v>
+        <v>152.9030320485913</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6841521275993</v>
+        <v>152.6829350947834</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7026507896244</v>
+        <v>152.7010489620461</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3889793675791</v>
+        <v>154.3870312628001</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3462442541914</v>
+        <v>155.3442980303583</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3345082785338</v>
+        <v>156.3323744999809</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9890719935068</v>
+        <v>157.9867205452605</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6060072648074</v>
+        <v>159.604011221453</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.448598878944</v>
+        <v>161.4472787852823</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9078449774957</v>
+        <v>159.9085313839573</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6253610646109</v>
+        <v>159.6256850018875</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2235865168022</v>
+        <v>159.2257917210351</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4773848117848</v>
+        <v>157.4802653719693</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0044323143417</v>
+        <v>158.007205959565</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3166302700789</v>
+        <v>158.319198628326</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3648869003654</v>
+        <v>158.3675103995386</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6026214991719</v>
+        <v>159.6051086748434</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4380425132422</v>
+        <v>158.4391547630626</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7146920004883</v>
+        <v>155.7137971719059</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8585104853907</v>
+        <v>155.8575560660971</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6606229511071</v>
+        <v>156.6602596083756</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.295026074002</v>
+        <v>156.2925807643918</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0609180005878</v>
+        <v>156.0583228317911</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8939374777253</v>
+        <v>155.8910818007943</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1575022486307</v>
+        <v>157.155798085813</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6603667069041</v>
+        <v>158.6608189557961</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1570032915449</v>
+        <v>159.1577268571118</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7507145319093</v>
+        <v>159.751700114495</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6078504534428</v>
+        <v>159.6080415470972</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.18216715842</v>
+        <v>160.1824799086351</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0495269241151</v>
+        <v>160.048887923344</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8284796771234</v>
+        <v>159.8272270789529</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3098722768896</v>
+        <v>160.3088100817743</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0181026199253</v>
+        <v>161.0165111025938</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6778318070373</v>
+        <v>161.6755714809729</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5339134616159</v>
+        <v>161.532290257527</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5107334044446</v>
+        <v>160.5114395584085</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0774326514899</v>
+        <v>160.0789110601215</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8966496775015</v>
+        <v>159.8987110189608</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9148081143892</v>
+        <v>159.9172630663859</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5872136626039</v>
+        <v>159.59187265152</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7347302803485</v>
+        <v>158.7431165878369</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.9490147399369</v>
+        <v>158.8456968471009</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.1775367007586</v>
+        <v>159.0581334761547</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.4284047603003</v>
+        <v>159.3003782353298</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.5814940968073</v>
+        <v>159.4325404636103</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.6267433642342</v>
+        <v>159.4840912099737</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.3191415917526</v>
+        <v>159.1739243347289</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.9594914573972</v>
+        <v>158.8085750828918</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.5363049715417</v>
+        <v>158.3879522294973</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.8377077919071</v>
+        <v>158.6624571485348</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.1021880267496</v>
+        <v>158.906015104664</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.6318189592514</v>
+        <v>159.2480991515711</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.2211243092382</v>
+        <v>155.0337499207591</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>149.4011636354959</v>
+        <v>149.8835658379703</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>151.9175658379703</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3048370637405</v>
+        <v>139.30404349761</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4729201935356</v>
+        <v>142.4717581313355</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7519673158247</v>
+        <v>143.7507064038484</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4302354145257</v>
+        <v>144.4289379098967</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.356597435204</v>
+        <v>144.3552779891402</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2782612511954</v>
+        <v>144.2769233690276</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2346730466131</v>
+        <v>144.2333278709946</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2740954268625</v>
+        <v>144.2727526679503</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9441458861182</v>
+        <v>144.9427972005129</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.036984450891</v>
+        <v>148.0370052989655</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315713832647</v>
+        <v>148.4315759052503</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535425864457</v>
+        <v>148.8535428129591</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9232372954413</v>
+        <v>148.923391049409</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2946768386045</v>
+        <v>149.29472623747</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4058257700355</v>
+        <v>150.4056179678936</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8565691757204</v>
+        <v>151.8560172521819</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2452339568258</v>
+        <v>152.2446460338908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5752644745544</v>
+        <v>152.5746942955127</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1762333131809</v>
+        <v>153.1758692768131</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.40837514621</v>
+        <v>152.408285617816</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9030320485913</v>
+        <v>152.9021680933379</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6829350947834</v>
+        <v>152.6817421014335</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.7010489620461</v>
+        <v>152.6994784781456</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3870312628001</v>
+        <v>154.385121161348</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3442980303583</v>
+        <v>155.342389534223</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3323744999809</v>
+        <v>156.3302819069744</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9867205452605</v>
+        <v>157.984414178226</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.604011221453</v>
+        <v>159.6020526998107</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4472787852823</v>
+        <v>161.4459829899469</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9085313839573</v>
+        <v>159.9092028098611</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6256850018875</v>
+        <v>159.6260013171066</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2257917210351</v>
+        <v>159.2279527197375</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4802653719693</v>
+        <v>157.4830888054855</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.007205959565</v>
+        <v>158.0099250872653</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.319198628326</v>
+        <v>158.3217170888105</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3675103995386</v>
+        <v>158.3700846731182</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6051086748434</v>
+        <v>159.6075497177016</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4391547630626</v>
+        <v>158.440247501977</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7137971719059</v>
+        <v>155.7129207008143</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8575560660971</v>
+        <v>155.8566212657339</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6602596083756</v>
+        <v>156.6599045746862</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2925807643918</v>
+        <v>156.2901826041865</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0583228317911</v>
+        <v>156.0557772878347</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8910818007943</v>
+        <v>155.8882797078539</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.155798085813</v>
+        <v>157.1541256063896</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6608189557961</v>
+        <v>158.6612629222673</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1577268571118</v>
+        <v>159.1584372903543</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.751700114495</v>
+        <v>159.7526678924411</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6080415470972</v>
+        <v>159.6082297458524</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1824799086351</v>
+        <v>160.1827879067164</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.048887923344</v>
+        <v>160.0482620736448</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8272270789529</v>
+        <v>159.8259988621352</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3088100817743</v>
+        <v>160.3077686069321</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0165111025938</v>
+        <v>161.0149501086009</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6755714809729</v>
+        <v>161.6733543764465</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.532290257527</v>
+        <v>161.5306958641434</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5114395584085</v>
+        <v>160.5121263166998</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0789110601215</v>
+        <v>160.0803568006235</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.8987110189608</v>
+        <v>159.9007302097029</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9172630663859</v>
+        <v>159.9196724425802</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.59187265152</v>
+        <v>159.5964443541932</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7431165878369</v>
+        <v>158.7513433972431</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.8456968471009</v>
+        <v>158.7499526736891</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.0581334761547</v>
+        <v>158.9485461244376</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.3003782353298</v>
+        <v>159.184222288033</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.4325404636103</v>
+        <v>159.2866157813025</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.4840912099737</v>
+        <v>159.3566022374898</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.1739243347289</v>
+        <v>159.0456396134243</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.8085750828918</v>
+        <v>158.6769591470844</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.3879522294973</v>
+        <v>158.2607907853535</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6624571485348</v>
+        <v>158.5139646657161</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.906015104664</v>
+        <v>158.745500565687</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.2480991515711</v>
+        <v>158.9195407944275</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.0337499207591</v>
+        <v>154.8952092317323</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>149.8835658379703</v>
+        <v>150.2866415390086</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>151.9175658379703</v>
+        <v>152.4500165390086</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7499526736891</v>
+        <v>158.7709843480741</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.9485461244376</v>
+        <v>158.9730689028625</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.184222288033</v>
+        <v>159.2116966098491</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2866157813025</v>
+        <v>159.3373329007042</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.3566022374898</v>
+        <v>159.3856229208282</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0456396134243</v>
+        <v>159.0771847062174</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.6769591470844</v>
+        <v>158.7124136434444</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.2607907853535</v>
+        <v>158.3004024445925</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.5139646657161</v>
+        <v>158.5607130104196</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.745500565687</v>
+        <v>158.8006224786443</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>158.9195407944275</v>
+        <v>159.1063348010387</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>154.8952092317323</v>
+        <v>155.1592303230085</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>150.2866415390086</v>
+        <v>150.4804444260855</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>152.4500165390086</v>
+        <v>152.7276319260856</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.30404349761</v>
+        <v>139.3032653390638</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4717581313355</v>
+        <v>142.4706185663339</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7507064038484</v>
+        <v>143.7494698023781</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4289379098967</v>
+        <v>144.427665318298</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3552779891402</v>
+        <v>144.3539838840748</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2769233690276</v>
+        <v>144.2756111882607</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2333278709946</v>
+        <v>144.2320085400422</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2727526679503</v>
+        <v>144.271435707646</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9427972005129</v>
+        <v>144.9414743195681</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0370052989655</v>
+        <v>148.037025736397</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315759052503</v>
+        <v>148.4315803355458</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535428129591</v>
+        <v>148.8535430315468</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.923391049409</v>
+        <v>148.9235417801122</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.29472623747</v>
+        <v>149.2947747225452</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4056179678936</v>
+        <v>150.4054142338719</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8560172521819</v>
+        <v>151.8554759502454</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2446460338908</v>
+        <v>152.244069399396</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5746942955127</v>
+        <v>152.574135001226</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1758692768131</v>
+        <v>153.1755121748659</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.408285617816</v>
+        <v>152.4081978367807</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9021680933379</v>
+        <v>152.9013211208868</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6817421014335</v>
+        <v>152.6805724429041</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6994784781456</v>
+        <v>152.6979384276175</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.385121161348</v>
+        <v>154.3832479629887</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.342389534223</v>
+        <v>155.3405176807417</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3302819069744</v>
+        <v>156.3282293204729</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.984414178226</v>
+        <v>157.982151611105</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6020526998107</v>
+        <v>159.6001306558898</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4459829899469</v>
+        <v>161.444710831628</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9092028098611</v>
+        <v>159.9098597347287</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6260013171066</v>
+        <v>159.6263102685165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2279527197375</v>
+        <v>159.230070826452</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4830888054855</v>
+        <v>157.4858567922199</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0099250872653</v>
+        <v>158.0125912858789</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3217170888105</v>
+        <v>158.324187087774</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3700846731182</v>
+        <v>158.3726110891561</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6075497177016</v>
+        <v>159.6099458937862</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.440247501977</v>
+        <v>158.4413212315687</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7129207008143</v>
+        <v>155.7120620297583</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8566212657339</v>
+        <v>155.8557054876938</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6599045746862</v>
+        <v>156.6595575747942</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2901826041865</v>
+        <v>156.2878302450036</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0557772878347</v>
+        <v>156.0532799619722</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8882797078539</v>
+        <v>155.8855297089585</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1541256063896</v>
+        <v>157.1524839376024</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6612629222673</v>
+        <v>158.6616988305169</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1584372903543</v>
+        <v>159.1591349433048</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7526678924411</v>
+        <v>159.7536183402579</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6082297458524</v>
+        <v>159.608415109543</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1827879067164</v>
+        <v>160.1830912519526</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0482620736448</v>
+        <v>160.0476489753946</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8259988621352</v>
+        <v>159.8247943228941</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3077686069321</v>
+        <v>160.3067472533484</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0149501086009</v>
+        <v>161.0134187712478</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6733543764465</v>
+        <v>161.6711792710128</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5306958641434</v>
+        <v>161.5291295349785</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5121263166998</v>
+        <v>160.5127943979647</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0803568006235</v>
+        <v>160.0817709111629</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9007302097029</v>
+        <v>159.9027084990425</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9196724425802</v>
+        <v>159.9220374640244</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.5964443541932</v>
+        <v>159.6009311503396</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7513433972431</v>
+        <v>158.7594151221953</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7709843480741</v>
+        <v>158.7539322802062</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.9730689028625</v>
+        <v>158.9548338749923</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.2116966098491</v>
+        <v>159.1973502421015</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.3373329007042</v>
+        <v>159.3212488593175</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.3856229208282</v>
+        <v>159.3725834272805</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0771847062174</v>
+        <v>159.076063795836</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7124136434444</v>
+        <v>158.725700232012</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.3004024445925</v>
+        <v>158.3360512391288</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.5607130104196</v>
+        <v>158.6065534444108</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.8006224786443</v>
+        <v>158.8788944371337</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.1063348010387</v>
+        <v>159.2019637209121</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.1592303230085</v>
+        <v>155.5752543804256</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>150.4804444260855</v>
+        <v>151.7450300176682</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>152.7276319260856</v>
+        <v>156.0449114618118</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3032653390638</v>
+        <v>139.302502143708</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4706185663339</v>
+        <v>142.4695008515304</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7494698023781</v>
+        <v>143.7482568151632</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.427665318298</v>
+        <v>144.4264169292033</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3539838840748</v>
+        <v>144.3527143970832</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2756111882607</v>
+        <v>144.274323975506</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2320085400422</v>
+        <v>144.2307143161881</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.271435707646</v>
+        <v>144.2701438096852</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9414743195681</v>
+        <v>144.9401765099764</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037025736397</v>
+        <v>148.0370457751937</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315803355458</v>
+        <v>148.4315846769044</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535430315468</v>
+        <v>148.8535432425357</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9235417801122</v>
+        <v>148.923689575821</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2947747225452</v>
+        <v>149.2948223188521</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4054142338719</v>
+        <v>150.4052144497352</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8554759502454</v>
+        <v>151.8549449663578</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.244069399396</v>
+        <v>152.2435037314804</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.574135001226</v>
+        <v>152.5735862831812</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1755121748659</v>
+        <v>153.1751618111897</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4081978367807</v>
+        <v>152.4081117524396</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9013211208868</v>
+        <v>152.9004906357113</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6805724429041</v>
+        <v>152.6794254417989</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6979384276175</v>
+        <v>152.6964279350402</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3832479629887</v>
+        <v>154.3814106095121</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3405176807417</v>
+        <v>155.3386814260276</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3282293204729</v>
+        <v>156.3262156059383</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.982151611105</v>
+        <v>157.9799316105911</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.6001306558898</v>
+        <v>159.5982440839104</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.444710831628</v>
+        <v>161.4434616726605</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9098597347287</v>
+        <v>159.910502618022</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6263102685165</v>
+        <v>159.6266121030699</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.230070826452</v>
+        <v>159.2321473032818</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4858567922199</v>
+        <v>157.4885709469382</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0125912858789</v>
+        <v>158.0152060828514</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.324187087774</v>
+        <v>158.3266100070091</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3726110891561</v>
+        <v>158.3750909656532</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6099458937862</v>
+        <v>159.6122984234557</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4413212315687</v>
+        <v>158.4423764366805</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7120620297583</v>
+        <v>155.7112206235643</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8557054876938</v>
+        <v>155.8548081592383</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6595575747942</v>
+        <v>156.6592183452697</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2878302450036</v>
+        <v>156.2855223893039</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0532799619722</v>
+        <v>156.0508295000088</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8855297089585</v>
+        <v>155.8828303687312</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1524839376024</v>
+        <v>157.1508722383533</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6616988305169</v>
+        <v>158.6621268967745</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1591349433048</v>
+        <v>159.1598201556151</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7536183402579</v>
+        <v>159.7545519158883</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.608415109543</v>
+        <v>159.6085976966291</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1830912519526</v>
+        <v>160.1833900412744</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0476489753946</v>
+        <v>160.0470482449199</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8247943228941</v>
+        <v>159.8236127842353</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3067472533484</v>
+        <v>160.3057454448241</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0134187712478</v>
+        <v>161.0119162562246</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6711792710128</v>
+        <v>161.6690449876867</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5291295349785</v>
+        <v>161.5275905485402</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5127943979647</v>
+        <v>160.5134444876556</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0817709111629</v>
+        <v>160.0831543874547</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9027084990425</v>
+        <v>159.9046470884845</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9220374640244</v>
+        <v>159.924359309961</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6009311503396</v>
+        <v>159.6053353357788</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7594151221953</v>
+        <v>158.7673360183169</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7539322802062</v>
+        <v>158.7373770832689</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.9548338749923</v>
+        <v>158.938226712203</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.1973502421015</v>
+        <v>159.1878882695078</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.3212488593175</v>
+        <v>159.3105268953666</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.3725834272805</v>
+        <v>159.365878740041</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.076063795836</v>
+        <v>159.0807734152548</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.725700232012</v>
+        <v>158.7440224710308</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.3360512391288</v>
+        <v>158.375559597108</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6065534444108</v>
+        <v>158.6570497133558</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.8788944371337</v>
+        <v>158.9633083444422</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.2019637209121</v>
+        <v>159.3049596738345</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.5752543804256</v>
+        <v>155.9641509244343</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>151.7450300176682</v>
+        <v>152.7939724580476</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>156.0449114618118</v>
+        <v>157.5064786350022</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.302502143708</v>
+        <v>139.3017534840753</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4695008515304</v>
+        <v>142.4684043644967</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7482568151632</v>
+        <v>143.7470667722852</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4264169292033</v>
+        <v>144.4251920588448</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3527143970832</v>
+        <v>144.3514688324734</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.274323975506</v>
+        <v>144.2730610250086</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2307143161881</v>
+        <v>144.2294444896591</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2701438096852</v>
+        <v>144.2688762655495</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9401765099764</v>
+        <v>144.9389030659453</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0370457751937</v>
+        <v>148.0370654269006</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315846769044</v>
+        <v>148.4315889319709</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535432425357</v>
+        <v>148.8535434462368</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.923689575821</v>
+        <v>148.9238345214038</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2948223188521</v>
+        <v>149.2948690505113</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4052144497352</v>
+        <v>150.405018501784</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8549449663578</v>
+        <v>151.8544240084192</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2435037314804</v>
+        <v>152.2429487203974</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5735862831812</v>
+        <v>152.5730478444066</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1751618111897</v>
+        <v>153.1748179969588</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4081117524396</v>
+        <v>152.4080273160682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9004906357113</v>
+        <v>152.8996761613647</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6794254417989</v>
+        <v>152.6783004466664</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6964279350402</v>
+        <v>152.6949461582221</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3814106095121</v>
+        <v>154.3796080827469</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3386814260276</v>
+        <v>155.3368797654207</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3262156059383</v>
+        <v>156.3242396712584</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9799316105911</v>
+        <v>157.9777529891492</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5982440839104</v>
+        <v>159.5963920145795</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4434616726605</v>
+        <v>161.4422348979835</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.910502618022</v>
+        <v>159.9111319001736</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6266121030699</v>
+        <v>159.6269070570247</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2321473032818</v>
+        <v>159.2341833633802</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4885709469382</v>
+        <v>157.491232822405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0152060828514</v>
+        <v>158.0177709475309</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3266100070091</v>
+        <v>158.3289871764088</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3750909656532</v>
+        <v>158.3775255728185</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6122984234557</v>
+        <v>159.6146084834177</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4423764366805</v>
+        <v>158.4434135860907</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7112206235643</v>
+        <v>155.7103959682408</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8548081592383</v>
+        <v>155.8539287303192</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6592183452697</v>
+        <v>156.6588866338786</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2855223893039</v>
+        <v>156.2832577880218</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0508295000088</v>
+        <v>156.0484245978762</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8828303687312</v>
+        <v>155.8801803038956</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1508722383533</v>
+        <v>157.1492896977868</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6621268967745</v>
+        <v>158.6625473296488</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1598201556151</v>
+        <v>159.1604932550917</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7545519158883</v>
+        <v>159.7554690614172</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6085976966291</v>
+        <v>159.6087775642179</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1833900412744</v>
+        <v>160.1836843692997</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0470482449199</v>
+        <v>160.0464595137126</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8236127842353</v>
+        <v>159.8224535946866</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3057454448241</v>
+        <v>160.3047626269033</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0119162562246</v>
+        <v>161.0104417601172</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6690449876867</v>
+        <v>161.6669503928588</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5275905485402</v>
+        <v>161.5260782073235</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5134444876556</v>
+        <v>160.5140772398565</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0831543874547</v>
+        <v>160.0845081848641</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9046470884845</v>
+        <v>159.9065471339404</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.924359309961</v>
+        <v>159.9266391195258</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6053353357788</v>
+        <v>159.6096591260157</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7673360183169</v>
+        <v>158.7751101900849</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7373770832689</v>
+        <v>158.6963897707432</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.938226712203</v>
+        <v>158.8936083528071</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.1878882695078</v>
+        <v>159.14856926866</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.3105268953666</v>
+        <v>159.2712112682486</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.365878740041</v>
+        <v>159.3245979151709</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0807734152548</v>
+        <v>159.0463443468821</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7440224710308</v>
+        <v>158.7172210474118</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.375559597108</v>
+        <v>158.363570224632</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6570497133558</v>
+        <v>158.6468308550317</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.9633083444422</v>
+        <v>158.9720007725263</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.3049596738345</v>
+        <v>159.3123934047644</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>155.9641509244343</v>
+        <v>156.1945223198257</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>152.7939724580476</v>
+        <v>153.4674617162669</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>157.5064786350022</v>
+        <v>157.4059688709228</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3017534840753</v>
+        <v>139.3010189488269</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4684043644967</v>
+        <v>142.4673285062214</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7470667722852</v>
+        <v>143.7458990289251</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4251920588448</v>
+        <v>144.4239900489654</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3514688324734</v>
+        <v>144.3502465205158</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2730610250086</v>
+        <v>144.2718216573582</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2294444896591</v>
+        <v>144.2281983771798</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2688762655495</v>
+        <v>144.2676323931718</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9389030659453</v>
+        <v>144.9376533079183</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0370654269006</v>
+        <v>148.037084702621</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315889319709</v>
+        <v>148.4315931032861</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535434462368</v>
+        <v>148.8535436429459</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9238345214038</v>
+        <v>148.9239766984889</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2948690505113</v>
+        <v>149.294914940782</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.405018501784</v>
+        <v>150.4048262806386</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8544240084192</v>
+        <v>151.8539127952467</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2429487203974</v>
+        <v>152.2424040679512</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5730478444066</v>
+        <v>152.5725193989379</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1748179969588</v>
+        <v>153.1744805503336</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4080273160682</v>
+        <v>152.4079444807902</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8996761613647</v>
+        <v>152.8988772395703</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6783004466664</v>
+        <v>152.6771968307711</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6949461582221</v>
+        <v>152.6934922866411</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3796080827469</v>
+        <v>154.3778394026864</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3368797654207</v>
+        <v>155.3351117316647</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3242396712584</v>
+        <v>156.3223004647864</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9777529891492</v>
+        <v>157.9756146029167</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5963920145795</v>
+        <v>159.5945735134584</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4422348979835</v>
+        <v>161.4410299141538</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9111319001736</v>
+        <v>159.9117480035544</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6269070570247</v>
+        <v>159.6271953565076</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2341833633802</v>
+        <v>159.2361801732966</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.491232822405</v>
+        <v>157.4938439123273</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0177709475309</v>
+        <v>158.0202872938989</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3289871764088</v>
+        <v>158.3313198763739</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3775255728185</v>
+        <v>158.3799161352085</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6146084834177</v>
+        <v>159.6168772086535</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4434135860907</v>
+        <v>158.4444331331584</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7103959682408</v>
+        <v>155.7095875699436</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8539287303192</v>
+        <v>155.8530666724693</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6588866338786</v>
+        <v>156.6585621990021</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2832577880218</v>
+        <v>156.281035238326</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0484245978762</v>
+        <v>156.0460639993398</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8801803038956</v>
+        <v>155.8775781809411</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1492896977868</v>
+        <v>157.147735533947</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6625473296488</v>
+        <v>158.6629603304582</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1604932550917</v>
+        <v>159.1611545582028</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7554690614172</v>
+        <v>159.7563702037453</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6087775642179</v>
+        <v>159.6089547680872</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1836843692997</v>
+        <v>160.1839743283789</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0464595137126</v>
+        <v>160.0458824276912</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8224535946866</v>
+        <v>159.8213161271082</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3047626269033</v>
+        <v>160.3037982658583</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0104417601172</v>
+        <v>161.0089945089946</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6669503928588</v>
+        <v>161.6648943943252</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5260782073235</v>
+        <v>161.5245918368494</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5140772398565</v>
+        <v>160.5146932789935</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0845081848641</v>
+        <v>160.0858332203885</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9065471339404</v>
+        <v>159.9084097478257</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9266391195258</v>
+        <v>159.9288779933732</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6096591260157</v>
+        <v>159.6139046596454</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7751101900849</v>
+        <v>158.7827415973418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.6963897707432</v>
+        <v>158.7050972484606</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8936083528071</v>
+        <v>158.8543489834424</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.14856926866</v>
+        <v>159.0936291042458</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2712112682486</v>
+        <v>159.2252406313791</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.3245979151709</v>
+        <v>159.2704828857928</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0463443468821</v>
+        <v>158.997665481074</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7172210474118</v>
+        <v>158.6757812008774</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.363570224632</v>
+        <v>158.3338651941548</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6468308550317</v>
+        <v>158.6151465790499</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.9720007725263</v>
+        <v>158.9305417897489</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.3123934047644</v>
+        <v>159.2777536781387</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.1945223198257</v>
+        <v>156.3437780598031</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>153.4674617162669</v>
+        <v>153.935289345885</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>157.4059688709228</v>
+        <v>157.1644058272306</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>155.8812346036634</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3010189488269</v>
+        <v>139.3002981419988</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4673285062214</v>
+        <v>142.4662727000189</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7458990289251</v>
+        <v>143.7447529641983</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4239900489654</v>
+        <v>144.42281026564</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3502465205158</v>
+        <v>144.3490468162436</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2718216573582</v>
+        <v>144.2706052182713</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2281983771798</v>
+        <v>144.2269753207476</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2676323931718</v>
+        <v>144.2664115357136</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9376533079183</v>
+        <v>144.9364265813684</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037084702621</v>
+        <v>148.037103613038</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315931032861</v>
+        <v>148.4315971932925</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535436429459</v>
+        <v>148.8535438329444</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9239766984889</v>
+        <v>148.9241161856181</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.294914940782</v>
+        <v>149.2949600121003</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4048262806386</v>
+        <v>150.404637681036</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8539127952467</v>
+        <v>151.8534110560704</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2424040679512</v>
+        <v>152.2418694869626</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5725193989379</v>
+        <v>152.572000671313</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1744805503336</v>
+        <v>153.17414929614</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4079444807902</v>
+        <v>152.4078632014903</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8988772395703</v>
+        <v>152.898093429365</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6771968307711</v>
+        <v>152.6761139909334</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6934922866411</v>
+        <v>152.6920655399708</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3778394026864</v>
+        <v>154.3761036257181</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3351117316647</v>
+        <v>155.3333763931847</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3223004647864</v>
+        <v>156.3203969734861</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9756146029167</v>
+        <v>157.9735153497182</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5945735134584</v>
+        <v>159.5927876794169</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4410299141538</v>
+        <v>161.4398461484102</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9117480035544</v>
+        <v>159.9123513333827</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6271953565076</v>
+        <v>159.6274772180436</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2361801732966</v>
+        <v>159.2381388551902</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4938439123273</v>
+        <v>157.4964056541312</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0202872938989</v>
+        <v>158.0227564831493</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3313198763739</v>
+        <v>158.333609340088</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3799161352085</v>
+        <v>158.3822638337521</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6168772086535</v>
+        <v>159.6191056942419</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4444331331584</v>
+        <v>158.4454355164389</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7095875699436</v>
+        <v>155.7087949540004</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8530666724693</v>
+        <v>155.8522214777573</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6585621990021</v>
+        <v>156.6582448090915</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.281035238326</v>
+        <v>156.2788535815033</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0460639993398</v>
+        <v>156.0437464938301</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8775781809411</v>
+        <v>155.875022713911</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.147735533947</v>
+        <v>157.1462089925058</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6629603304582</v>
+        <v>158.6633660935444</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1611545582028</v>
+        <v>159.1618043705613</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7563702037453</v>
+        <v>159.7572557552294</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6089547680872</v>
+        <v>159.6091293627098</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1839743283789</v>
+        <v>160.1842600086429</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0458824276912</v>
+        <v>160.0453166465044</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8213161271082</v>
+        <v>159.8201997775695</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3037982658583</v>
+        <v>160.3028518477331</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0089945089946</v>
+        <v>161.0075737570743</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6648943943252</v>
+        <v>161.6628759394224</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5245918368494</v>
+        <v>161.523130784748</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5146932789935</v>
+        <v>160.5152932014364</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0858332203885</v>
+        <v>160.0871303745246</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9084097478257</v>
+        <v>159.910236001045</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9288779933732</v>
+        <v>159.9310769952269</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6139046596454</v>
+        <v>159.618074001589</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7827415973418</v>
+        <v>158.7902340614809</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7050972484606</v>
+        <v>158.7136530913482</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8543489834424</v>
+        <v>158.8380881388219</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0936291042458</v>
+        <v>159.0658001831204</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2252406313791</v>
+        <v>159.2073872690539</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.2704828857928</v>
+        <v>159.2632311930839</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.997665481074</v>
+        <v>158.9944594030592</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.6757812008774</v>
+        <v>158.682124018424</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.3338651941548</v>
+        <v>158.3545883838529</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6151465790499</v>
+        <v>158.6407925961096</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.9305417897489</v>
+        <v>158.9569173266562</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.2777536781387</v>
+        <v>159.327439285867</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.3437780598031</v>
+        <v>156.5828000218009</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>153.935289345885</v>
+        <v>154.4889567528718</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>157.1644058272306</v>
+        <v>157.6948345449427</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>155.8812346036634</v>
+        <v>158.3663570554945</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3002981419988</v>
+        <v>139.2995906822901</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4662727000189</v>
+        <v>142.4652363904993</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7447529641983</v>
+        <v>143.7436279800552</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.42281026564</v>
+        <v>144.421652098162</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3490468162436</v>
+        <v>144.3478690983191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2706052182713</v>
+        <v>144.2694110774407</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2269753207476</v>
+        <v>144.2257746864757</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2664115357136</v>
+        <v>144.2652130604097</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9364265813684</v>
+        <v>144.935222255656</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037103613038</v>
+        <v>148.0371221684338</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4315971932925</v>
+        <v>148.4316012043386</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535438329444</v>
+        <v>148.8535440165003</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9241161856181</v>
+        <v>148.924253058391</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2949600121003</v>
+        <v>149.2950042861149</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.404637681036</v>
+        <v>150.4044526016388</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8534110560704</v>
+        <v>151.8529185300555</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2418694869626</v>
+        <v>152.2413447007664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.572000671313</v>
+        <v>152.5714913960946</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.17414929614</v>
+        <v>153.1738240655677</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4078632014903</v>
+        <v>152.4077834347327</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.898093429365</v>
+        <v>152.8973243062889</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6761139909334</v>
+        <v>152.6750513464339</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6920655399708</v>
+        <v>152.6906651666888</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3761036257181</v>
+        <v>154.3743998429522</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3333763931847</v>
+        <v>155.3316728524587</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3203969734861</v>
+        <v>156.3185282211799</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9735153497182</v>
+        <v>157.9714541671876</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5927876794169</v>
+        <v>159.5910336431688</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4398461484102</v>
+        <v>161.4386830477857</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9123513333827</v>
+        <v>159.9129422785802</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6274772180436</v>
+        <v>159.6277528490521</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2381388551902</v>
+        <v>159.2400604889177</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4964056541312</v>
+        <v>157.4989194315841</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0227564831493</v>
+        <v>158.0251798261237</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.333609340088</v>
+        <v>158.3358567556692</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3822638337521</v>
+        <v>158.3845698076697</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6191056942419</v>
+        <v>159.6212949970887</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4454355164389</v>
+        <v>158.4464211602702</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7087949540004</v>
+        <v>155.7080176639919</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8522214777573</v>
+        <v>155.851392657803</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6582448090915</v>
+        <v>156.6579342421559</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2788535815033</v>
+        <v>156.2767117009582</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0437464938301</v>
+        <v>156.0414709143913</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.875022713911</v>
+        <v>155.8725126623079</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1462089925058</v>
+        <v>157.1447093455578</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6633660935444</v>
+        <v>158.6637648065696</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1618043705613</v>
+        <v>159.1624429873823</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7572557552294</v>
+        <v>159.7581261142902</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6091293627098</v>
+        <v>159.6093014012782</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1842600086429</v>
+        <v>160.1845414980495</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0453166465044</v>
+        <v>160.0447618428755</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8201997775695</v>
+        <v>159.8191039642867</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3028518477331</v>
+        <v>160.3019228774375</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0075737570743</v>
+        <v>161.0061787854576</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6628759394224</v>
+        <v>161.6608940132615</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.523130784748</v>
+        <v>161.5216944198835</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5152932014364</v>
+        <v>160.5158775770005</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0871303745246</v>
+        <v>160.0884004930305</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.910236001045</v>
+        <v>159.9120269248712</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9310769952269</v>
+        <v>159.9332371533599</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.618074001589</v>
+        <v>159.6221691461736</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7902340614809</v>
+        <v>158.7975912713243</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7136530913482</v>
+        <v>158.7220611184806</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8380881388219</v>
+        <v>158.8462365634454</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0658001831204</v>
+        <v>159.0674756781183</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2073872690539</v>
+        <v>159.2205365513352</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.2632311930839</v>
+        <v>159.2884025220711</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9944594030592</v>
+        <v>159.0270015466165</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.682124018424</v>
+        <v>158.7289015315687</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.3545883838529</v>
+        <v>158.4204341900198</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6407925961096</v>
+        <v>158.7195637833008</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.9569173266562</v>
+        <v>159.0473714013447</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.327439285867</v>
+        <v>159.4570289364607</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.5828000218009</v>
+        <v>156.9074414225872</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>154.4889567528718</v>
+        <v>155.1256089442966</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>157.6948345449427</v>
+        <v>158.3781135183941</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>158.3663570554945</v>
+        <v>159.9634139633482</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2995906822901</v>
+        <v>139.2988962023908</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4652363904993</v>
+        <v>142.4642190425941</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7436279800552</v>
+        <v>143.7425235002408</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.421652098162</v>
+        <v>144.4205149579904</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3478690983191</v>
+        <v>144.3467127679615</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2694110774407</v>
+        <v>144.2682386274474</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2257746864757</v>
+        <v>144.2245958634981</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2652130604097</v>
+        <v>144.2640363574754</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.935222255656</v>
+        <v>144.9340397229495</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371221684338</v>
+        <v>148.0371403787087</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316012043386</v>
+        <v>148.4316051386837</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535440165003</v>
+        <v>148.8535441938689</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.924253058391</v>
+        <v>148.9243873896016</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2950042861149</v>
+        <v>149.295047783721</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4044526016388</v>
+        <v>150.404270944853</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8529185300555</v>
+        <v>151.852434965851</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2413447007664</v>
+        <v>152.2408294427337</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5714913960946</v>
+        <v>152.5709913174187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1738240655677</v>
+        <v>153.1735046958831</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4077834347327</v>
+        <v>152.4077051386835</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8973243062889</v>
+        <v>152.8965694616215</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6750513464339</v>
+        <v>152.6740083379783</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6906651666888</v>
+        <v>152.6892904427603</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3743998429522</v>
+        <v>154.3727271786394</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3316728524587</v>
+        <v>155.3300002444781</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3185282211799</v>
+        <v>156.316693266889</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9714541671876</v>
+        <v>157.969430030991</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5910336431688</v>
+        <v>159.589310565883</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4386830477857</v>
+        <v>161.4375400782648</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9129422785802</v>
+        <v>159.9135212125764</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6277528490521</v>
+        <v>159.6280224483133</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2400604889177</v>
+        <v>159.2419461140049</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.4989194315841</v>
+        <v>157.501386577272</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0251798261237</v>
+        <v>158.0275585856146</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3358567556692</v>
+        <v>158.3380632682038</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3845698076697</v>
+        <v>158.3868351562921</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6212949970887</v>
+        <v>159.6234461375676</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4464211602702</v>
+        <v>158.4473904753335</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7080176639919</v>
+        <v>155.7072552608845</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.851392657803</v>
+        <v>155.8505797428478</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6579342421559</v>
+        <v>156.6576302852802</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2767117009582</v>
+        <v>156.2746085203185</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0414709143913</v>
+        <v>156.0392361357387</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8725126623079</v>
+        <v>155.8700468291082</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1447093455578</v>
+        <v>157.1432358904762</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6637648065696</v>
+        <v>158.6641566508</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1624429873823</v>
+        <v>159.1630706939183</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7581261142902</v>
+        <v>159.7589816659919</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6093014012782</v>
+        <v>159.6094709357303</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1845414980495</v>
+        <v>160.1848188824318</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0447618428755</v>
+        <v>160.0442177019821</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8191039642867</v>
+        <v>159.8180281266185</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3019228774375</v>
+        <v>160.3010108778916</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0061787854576</v>
+        <v>161.0048089009339</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6608940132615</v>
+        <v>161.6589476370567</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5216944198835</v>
+        <v>161.5202821315191</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5158775770005</v>
+        <v>160.5164469503563</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0884004930305</v>
+        <v>160.0896443885882</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9120269248712</v>
+        <v>159.9137835127262</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9332371533599</v>
+        <v>159.9353594620067</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6221691461736</v>
+        <v>159.6261920200604</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.7975912713243</v>
+        <v>158.8048167887094</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7220611184806</v>
+        <v>158.7303250256412</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8462365634454</v>
+        <v>158.853829568139</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0674756781183</v>
+        <v>159.0718130403692</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2205365513352</v>
+        <v>159.2367161504422</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.2884025220711</v>
+        <v>159.307329259882</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0270015466165</v>
+        <v>159.0610105478908</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7289015315687</v>
+        <v>158.7772718208032</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4204341900198</v>
+        <v>158.4878606949593</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7195637833008</v>
+        <v>158.8006328108329</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.0473714013447</v>
+        <v>159.1408524473584</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.4570289364607</v>
+        <v>159.5882015411031</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>156.9074414225872</v>
+        <v>157.2167726872575</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>155.1256089442966</v>
+        <v>155.6988182097409</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.3781135183941</v>
+        <v>158.9486473189486</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>159.9634139633482</v>
+        <v>160.8536495089272</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.853829568139</v>
+        <v>158.8211365146808</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0718130403692</v>
+        <v>159.0340645610173</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.2367161504422</v>
+        <v>159.1948294495711</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.307329259882</v>
+        <v>159.2600576861949</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0610105478908</v>
+        <v>159.0105129262122</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7772718208032</v>
+        <v>158.7211263417196</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4878606949593</v>
+        <v>158.4255343735391</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.8006328108329</v>
+        <v>158.728089977741</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.1408524473584</v>
+        <v>159.0544575741816</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.5882015411031</v>
+        <v>159.4789685293565</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.2167726872575</v>
+        <v>157.0763706444406</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>155.6988182097409</v>
+        <v>155.4940009972516</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.9486473189486</v>
+        <v>158.6073785722733</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>160.8536495089272</v>
+        <v>159.197581859089</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2988962023908</v>
+        <v>139.2982143483456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4642190425941</v>
+        <v>142.4632201406353</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7425235002408</v>
+        <v>143.7414389693106</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4205149579904</v>
+        <v>144.4193982777528</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3467127679615</v>
+        <v>144.345577247933</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2682386274474</v>
+        <v>144.2670872827312</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2245958634981</v>
+        <v>144.2234382629343</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2640363574754</v>
+        <v>144.262880839073</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9340397229495</v>
+        <v>144.9328783972039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371403787087</v>
+        <v>148.037158253398</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316051386837</v>
+        <v>148.4316089985016</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535441938689</v>
+        <v>148.8535443652936</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9243873896016</v>
+        <v>148.9245192493669</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295047783721</v>
+        <v>149.295090525093</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.404270944853</v>
+        <v>150.4040926166575</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.852434965851</v>
+        <v>151.8519601211629</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2408294427337</v>
+        <v>152.2403234558214</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5709913174187</v>
+        <v>152.5705001885672</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1735046958831</v>
+        <v>153.1731910301594</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4077051386835</v>
+        <v>152.4076282730373</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8965694616215</v>
+        <v>152.895828501659</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6740083379783</v>
+        <v>152.6729844267196</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6892904427603</v>
+        <v>152.6879406703937</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3727271786394</v>
+        <v>154.3710847886761</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3300002444781</v>
+        <v>155.32835773529</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.316693266889</v>
+        <v>156.3148912032648</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.969430030991</v>
+        <v>157.9674419531432</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.589310565883</v>
+        <v>159.587617637867</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4375400782648</v>
+        <v>161.4364167239829</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9135212125764</v>
+        <v>159.9140884940674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6280224483133</v>
+        <v>159.6282862064067</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2419461140049</v>
+        <v>159.2437967315097</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.501386577272</v>
+        <v>157.5038083749405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0275585856146</v>
+        <v>158.0298939785429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3380632682038</v>
+        <v>158.3402299816732</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3868351562921</v>
+        <v>158.3890609407858</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6234461375676</v>
+        <v>159.6255601010777</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4473904753335</v>
+        <v>158.4483438591864</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7072552608845</v>
+        <v>155.706507322213</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8505797428478</v>
+        <v>155.8497822808783</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6576302852802</v>
+        <v>156.6573327341726</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2746085203185</v>
+        <v>156.2725430016439</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0392361357387</v>
+        <v>156.0370410724192</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8700468291082</v>
+        <v>155.8676240588798</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1432358904762</v>
+        <v>157.141787948829</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6641566508</v>
+        <v>158.6645418013738</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1630706939183</v>
+        <v>159.1636877658732</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7589816659919</v>
+        <v>159.7598227825914</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6094709357303</v>
+        <v>159.609638016775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1848188824318</v>
+        <v>160.1850922455459</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0442177019821</v>
+        <v>160.043683920873</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8180281266185</v>
+        <v>159.8169717241156</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3010108778916</v>
+        <v>160.3001153892157</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0048089009339</v>
+        <v>161.0034634348467</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6589476370567</v>
+        <v>161.6570358665401</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5202821315191</v>
+        <v>161.5188933285192</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5164469503563</v>
+        <v>160.5170018423518</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0896443885882</v>
+        <v>160.0908628423728</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9137835127262</v>
+        <v>159.915506721868</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9353594620067</v>
+        <v>159.9374448827128</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6261920200604</v>
+        <v>159.630144485033</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8048167887094</v>
+        <v>158.8119140538025</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7303250256412</v>
+        <v>158.7384483900797</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8211365146808</v>
+        <v>158.7968876936682</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0340645610173</v>
+        <v>159.0018562613276</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.1948294495711</v>
+        <v>159.1700062143632</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.2600576861949</v>
+        <v>159.23274915425</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>159.0105129262122</v>
+        <v>158.9946335343439</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7211263417196</v>
+        <v>158.7136321267051</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4255343735391</v>
+        <v>158.4303172883246</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.728089977741</v>
+        <v>158.7360664140289</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.0544575741816</v>
+        <v>159.0610063279658</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.4789685293565</v>
+        <v>159.4991347716385</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.0763706444406</v>
+        <v>157.2298974723396</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>155.4940009972516</v>
+        <v>155.8154090687702</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.6073785722733</v>
+        <v>158.7904572912711</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>159.197581859089</v>
+        <v>158.7384942769376</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2982143483456</v>
+        <v>139.2975447789526</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4632201406353</v>
+        <v>142.4622391874844</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7414389693106</v>
+        <v>143.7403738517004</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4193982777528</v>
+        <v>144.4183015103029</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.345577247933</v>
+        <v>144.3444619815785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2670872827312</v>
+        <v>144.2659564786166</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2234382629343</v>
+        <v>144.2223013169091</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.262880839073</v>
+        <v>144.261745938333</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9328783972039</v>
+        <v>144.9317377131939</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037158253398</v>
+        <v>148.0371758016897</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316089985016</v>
+        <v>148.4316127858852</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535443652936</v>
+        <v>148.8535445310061</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9245192493669</v>
+        <v>148.924648705249</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295090525093</v>
+        <v>149.2951325297149</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4040926166575</v>
+        <v>150.4039175264422</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8519601211629</v>
+        <v>151.8514937623499</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2403234558214</v>
+        <v>152.2398264921461</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5705001885672</v>
+        <v>152.570017771563</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1731910301594</v>
+        <v>153.1728829170195</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4076282730373</v>
+        <v>152.4075527989486</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.895828501659</v>
+        <v>152.8951010470314</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6729844267196</v>
+        <v>152.6719790933324</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6879406703937</v>
+        <v>152.6866151768635</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3710847886761</v>
+        <v>154.3694718591886</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.32835773529</v>
+        <v>155.3267445206177</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3148912032648</v>
+        <v>156.3131211551009</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9674419531432</v>
+        <v>157.9654889804128</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.587617637867</v>
+        <v>159.5859540773176</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4364167239829</v>
+        <v>161.4353124864661</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9140884940674</v>
+        <v>159.9146444677294</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6282862064067</v>
+        <v>159.628544306123</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2437967315097</v>
+        <v>159.245613305782</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5038083749405</v>
+        <v>157.5061860617091</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0298939785429</v>
+        <v>158.0321871780181</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3402299816732</v>
+        <v>158.3423579607772</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3890609407858</v>
+        <v>158.3912481857884</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6255601010777</v>
+        <v>159.6276378395223</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4483438591864</v>
+        <v>158.4492816967742</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.706507322213</v>
+        <v>155.7057734413073</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8497822808783</v>
+        <v>155.8489998367984</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6573327341726</v>
+        <v>156.6570413927372</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2725430016439</v>
+        <v>156.2705141437275</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0370410724192</v>
+        <v>156.034884677068</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8676240588798</v>
+        <v>155.8652432359956</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.141787948829</v>
+        <v>157.1403648653492</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6645418013738</v>
+        <v>158.6649204275562</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1636877658732</v>
+        <v>159.1642944697953</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7598227825914</v>
+        <v>159.7606498240619</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.609638016775</v>
+        <v>159.6098026939189</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1850922455459</v>
+        <v>160.185361669119</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.043683920873</v>
+        <v>160.0431602079147</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8169717241156</v>
+        <v>159.8159342356218</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3001153892157</v>
+        <v>160.299235967964</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0034634348467</v>
+        <v>161.0021417420194</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6570358665401</v>
+        <v>161.6551577904605</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5188933285192</v>
+        <v>161.5175274385881</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5170018423518</v>
+        <v>160.5175427512549</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0908628423728</v>
+        <v>160.0920566055354</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.915506721868</v>
+        <v>159.9171974749902</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9374448827128</v>
+        <v>159.9394943456218</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.630144485033</v>
+        <v>159.6340283406509</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8119140538025</v>
+        <v>158.8188863901513</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7384483900797</v>
+        <v>158.7464346750616</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7968876936682</v>
+        <v>158.7649178277319</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0018562613276</v>
+        <v>158.9598736599604</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.1700062143632</v>
+        <v>159.133856668212</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.23274915425</v>
+        <v>159.1929916218121</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9946335343439</v>
+        <v>158.964872357694</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7136321267051</v>
+        <v>158.690433488561</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4303172883246</v>
+        <v>158.4171932204277</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7360664140289</v>
+        <v>158.7232616731312</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.0610063279658</v>
+        <v>159.0433799175522</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.4991347716385</v>
+        <v>159.4886315602019</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.2298974723396</v>
+        <v>157.3340023467362</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>155.8154090687702</v>
+        <v>156.0486506262752</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.7904572912711</v>
+        <v>158.5448190421995</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>158.7384942769376</v>
+        <v>158.2953899118239</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2975447789526</v>
+        <v>139.2968871651942</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4622391874844</v>
+        <v>142.4612757037071</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7403738517004</v>
+        <v>143.7393276308444</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4183015103029</v>
+        <v>144.4172241278273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3444619815785</v>
+        <v>144.3433664319168</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2659564786166</v>
+        <v>144.2648456703897</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2223013169091</v>
+        <v>144.2211844776249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.261745938333</v>
+        <v>144.2606311084284</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9317377131939</v>
+        <v>144.9306171255971</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371758016897</v>
+        <v>148.0371930324391</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316127858852</v>
+        <v>148.4316165028498</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535445310061</v>
+        <v>148.8535446912275</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.924648705249</v>
+        <v>148.9247758223706</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2951325297149</v>
+        <v>149.2951738164097</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4039175264422</v>
+        <v>150.4037455868544</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8514937623499</v>
+        <v>151.8510356640408</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2398264921461</v>
+        <v>152.239338312579</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.570017771563</v>
+        <v>152.5695438367867</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1728829170195</v>
+        <v>153.1725802103926</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4075527989486</v>
+        <v>152.4074786789654</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8951010470314</v>
+        <v>152.8943867320564</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6719790933324</v>
+        <v>152.6709918371379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6866151768635</v>
+        <v>152.6853133133952</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3694718591886</v>
+        <v>154.3678876051931</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3267445206177</v>
+        <v>155.3251598245541</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3131211551009</v>
+        <v>156.3113822779254</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9654889804128</v>
+        <v>157.9635701928103</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5859540773176</v>
+        <v>159.584319129135</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4353124864661</v>
+        <v>161.4342268839084</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9146444677294</v>
+        <v>159.9151894648929</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.628544306123</v>
+        <v>159.6287969228526</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.245613305782</v>
+        <v>159.2473967661288</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5061860617091</v>
+        <v>157.5085208301662</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0321871780181</v>
+        <v>158.0344393152893</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3423579607772</v>
+        <v>158.3444482326613</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3912481857884</v>
+        <v>158.3933978809634</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6276378395223</v>
+        <v>159.6296802727138</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4492816967742</v>
+        <v>158.4502043609164</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7057734413073</v>
+        <v>155.7050532265634</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8489998367984</v>
+        <v>155.8482319916475</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6570413927372</v>
+        <v>156.6567560726728</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2705141437275</v>
+        <v>156.2685209804886</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.034884677068</v>
+        <v>156.0327659387557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8652432359956</v>
+        <v>155.8629032829395</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1403648653492</v>
+        <v>157.1389660069574</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6649204275562</v>
+        <v>158.6652926929829</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1642944697953</v>
+        <v>159.1648910634522</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7606498240619</v>
+        <v>159.7614631385916</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6098026939189</v>
+        <v>159.6099650154917</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.185361669119</v>
+        <v>160.1856272328968</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0431602079147</v>
+        <v>160.0426462822711</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8159342356218</v>
+        <v>159.8149151584213</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.299235967964</v>
+        <v>160.2983721863977</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0021417420194</v>
+        <v>161.0008431997373</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6551577904605</v>
+        <v>161.6533125291578</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5175274385881</v>
+        <v>161.5161839075427</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5175427512549</v>
+        <v>160.5180701539202</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0920566055354</v>
+        <v>160.0932264006042</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9171974749902</v>
+        <v>159.9188566617387</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9394943456218</v>
+        <v>159.941508750706</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6340283406509</v>
+        <v>159.6378453267776</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8188863901513</v>
+        <v>158.8257370094941</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7464346750616</v>
+        <v>158.7542872342173</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7649178277319</v>
+        <v>158.7724996939818</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.9598736599604</v>
+        <v>158.9191205097944</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.133856668212</v>
+        <v>159.0893770072579</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.1929916218121</v>
+        <v>159.1477033004726</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.964872357694</v>
+        <v>158.9339856674405</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.690433488561</v>
+        <v>158.6786755175079</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4171932204277</v>
+        <v>158.4279491276146</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7232616731312</v>
+        <v>158.7487392940167</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.0433799175522</v>
+        <v>159.0809286574356</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.4886315602019</v>
+        <v>159.5346250119122</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.3340023467362</v>
+        <v>157.5367845219221</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>156.0486506262752</v>
+        <v>156.4174373297903</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.5448190421995</v>
+        <v>158.9008746812963</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>158.2953899118239</v>
+        <v>158.991723441726</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>161.238910941726</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2968871651942</v>
+        <v>139.2962411896976</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4612757037071</v>
+        <v>142.4603292267925</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7393276308444</v>
+        <v>143.7382998083404</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4172241278273</v>
+        <v>144.4161656209991</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3433664319168</v>
+        <v>144.342290080779</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2648456703897</v>
+        <v>144.2637543324245</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2211844776249</v>
+        <v>144.2200872164818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2606311084284</v>
+        <v>144.259535821696</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9306171255971</v>
+        <v>144.9295161081265</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371930324391</v>
+        <v>148.0372099541842</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316165028498</v>
+        <v>148.4316201513367</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535446912275</v>
+        <v>148.8535448461689</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9247758223706</v>
+        <v>148.9249006635237</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2951738164097</v>
+        <v>149.2952144033669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4037455868544</v>
+        <v>150.4035767136539</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8510356640408</v>
+        <v>151.850585608772</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.239338312579</v>
+        <v>152.2388586863635</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5695438367867</v>
+        <v>152.5690781626131</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1725802103926</v>
+        <v>153.1722827692848</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4074786789654</v>
+        <v>152.4074058769682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8943867320564</v>
+        <v>152.8936852041283</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6709918371379</v>
+        <v>152.6700221752745</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6853133133952</v>
+        <v>152.6840344541098</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3678876051931</v>
+        <v>154.3663312693258</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3251598245541</v>
+        <v>155.3236028983225</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3113822779254</v>
+        <v>156.309673756665</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9635701928103</v>
+        <v>157.9616847021549</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.584319129135</v>
+        <v>159.5827120637965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4342268839084</v>
+        <v>161.4331594504844</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9151894648929</v>
+        <v>159.9157238041773</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6287969228526</v>
+        <v>159.6290442249504</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2473967661288</v>
+        <v>159.2491480083893</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5085208301662</v>
+        <v>157.5108138303517</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0344393152893</v>
+        <v>158.0366514815926</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3444482326613</v>
+        <v>158.3465017885545</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3933978809634</v>
+        <v>158.395510982474</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6296802727138</v>
+        <v>159.6316882897088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4502043609164</v>
+        <v>158.4511122127715</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7050532265634</v>
+        <v>155.7043463007535</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8482319916475</v>
+        <v>155.8474783418609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6567560726728</v>
+        <v>156.6564765930944</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2685209804886</v>
+        <v>156.2665625794468</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0327659387557</v>
+        <v>156.0306838814209</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8629032829395</v>
+        <v>155.8606031586961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1389660069574</v>
+        <v>157.1375907618337</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6652926929829</v>
+        <v>158.6656587558901</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1648910634522</v>
+        <v>159.1654777961861</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7614631385916</v>
+        <v>159.7622630630581</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6099650154917</v>
+        <v>159.6101250286733</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1856272328968</v>
+        <v>160.1858890146912</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0426462822711</v>
+        <v>160.0421418734097</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8149151584213</v>
+        <v>159.8139140074317</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2983721863977</v>
+        <v>160.2975236317981</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0008431997373</v>
+        <v>160.9995672067813</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6533125291578</v>
+        <v>161.6514992332116</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5161839075427</v>
+        <v>161.5148621986175</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5180701539202</v>
+        <v>160.5185845068874</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0932264006042</v>
+        <v>160.0943729228092</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9188566617387</v>
+        <v>159.9204851401512</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.941508750706</v>
+        <v>159.9434889689412</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6378453267776</v>
+        <v>159.6415971259883</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8257370094941</v>
+        <v>158.832469016337</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7542872342173</v>
+        <v>158.7620093157038</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7724996939818</v>
+        <v>158.7799631245588</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.9191205097944</v>
+        <v>158.87973977453</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0893770072579</v>
+        <v>159.0461484950097</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.1477033004726</v>
+        <v>159.1022886634227</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9339856674405</v>
+        <v>158.8984243995172</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.6786755175079</v>
+        <v>158.6609508973027</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4279491276146</v>
+        <v>158.4300774236558</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7487392940167</v>
+        <v>158.7624085482501</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.0809286574356</v>
+        <v>159.103119198932</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.5346250119122</v>
+        <v>159.560668716952</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.5367845219221</v>
+        <v>157.6977548734313</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>156.4174373297903</v>
+        <v>156.7100380148984</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.9008746812963</v>
+        <v>159.1447426345038</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>158.991723441726</v>
+        <v>159.4157648339009</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>161.238910941726</v>
+        <v>161.6629523339009</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.87973977453</v>
+        <v>158.9014346862271</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0461484950097</v>
+        <v>159.0698088483715</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.1022886634227</v>
+        <v>159.1274296111388</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.8984243995172</v>
+        <v>158.9321553679468</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.6609508973027</v>
+        <v>158.6957674801799</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4300774236558</v>
+        <v>158.4665676074175</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.7624085482501</v>
+        <v>158.8031883988871</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.103119198932</v>
+        <v>159.1500769339969</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.560668716952</v>
+        <v>159.6163816760279</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.6977548734313</v>
+        <v>157.767239794447</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>156.7100380148984</v>
+        <v>156.8041948516477</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.1447426345038</v>
+        <v>159.2824579488756</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>159.4157648339009</v>
+        <v>159.641368141168</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>161.6629523339009</v>
+        <v>161.888555641168</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2962411896976</v>
+        <v>139.2956065462247</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4603292267925</v>
+        <v>142.4593993104129</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7382998083404</v>
+        <v>143.7372899031585</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4161656209991</v>
+        <v>144.4151254981757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.342290080779</v>
+        <v>144.3412324279917</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2637543324245</v>
+        <v>144.262681957354</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2200872164818</v>
+        <v>144.2190090232445</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.259535821696</v>
+        <v>144.2584595688052</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9295161081265</v>
+        <v>144.928434152707</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0372099541842</v>
+        <v>148.03722657516</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316201513367</v>
+        <v>148.4316237332169</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535448461689</v>
+        <v>148.8535449960316</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9249006635237</v>
+        <v>148.9250232892729</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2952144033669</v>
+        <v>149.295254308169</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4035767136539</v>
+        <v>150.4034108255757</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.850585608772</v>
+        <v>151.8501433866436</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2388586863635</v>
+        <v>152.238387390752</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5690781626131</v>
+        <v>152.5686205350662</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1722827692848</v>
+        <v>153.1719904575597</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4074058769682</v>
+        <v>152.4073343581107</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8936852041283</v>
+        <v>152.8929961231383</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6700221752745</v>
+        <v>152.6690696419136</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6840344541098</v>
+        <v>152.6827779950231</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3663312693258</v>
+        <v>154.3648021206403</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3236028983225</v>
+        <v>155.3220730191034</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.309673756665</v>
+        <v>156.3079948043785</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9616847021549</v>
+        <v>157.9598316507133</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5827120637965</v>
+        <v>159.5811321762869</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4331594504844</v>
+        <v>161.4321097356958</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9157238041773</v>
+        <v>159.9162477920906</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6290442249504</v>
+        <v>159.6292863740798</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2491480083893</v>
+        <v>159.2508678964255</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5108138303517</v>
+        <v>157.5130661716358</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0366514815926</v>
+        <v>158.0388247299012</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3465017885545</v>
+        <v>158.3485195853218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.395510982474</v>
+        <v>158.3975884143846</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6316882897088</v>
+        <v>159.6336627500769</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4511122127715</v>
+        <v>158.4520056022824</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7043463007535</v>
+        <v>155.7036523003736</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8474783418609</v>
+        <v>155.8467384985716</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6564765930944</v>
+        <v>156.6562027801758</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2665625794468</v>
+        <v>156.2646380402765</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0306838814209</v>
+        <v>156.0286375623827</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8606031586961</v>
+        <v>155.858341857223</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1375907618337</v>
+        <v>157.1362385385345</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6656587558901</v>
+        <v>158.6660187693344</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1654777961861</v>
+        <v>159.1660549092541</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7622630630581</v>
+        <v>159.7630499234799</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6101250286733</v>
+        <v>159.6102827795196</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1858890146912</v>
+        <v>160.1861470904266</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0421418734097</v>
+        <v>160.0416467206354</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8139140074317</v>
+        <v>159.8129303144389</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2975236317981</v>
+        <v>160.2966899058135</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.9995672067813</v>
+        <v>160.998313182511</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6514992332116</v>
+        <v>161.6497170821581</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5148621986175</v>
+        <v>161.5135617918</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5185845068874</v>
+        <v>160.5190862474127</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0943729228092</v>
+        <v>160.095496841335</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9204851401512</v>
+        <v>159.9220837380233</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9434889689412</v>
+        <v>159.945435843429</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6415971259883</v>
+        <v>159.6452853658647</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.832469016337</v>
+        <v>158.8390854123127</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7620093157038</v>
+        <v>158.7696040661846</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7799631245588</v>
+        <v>158.7873107691646</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.9014346862271</v>
+        <v>158.8781927754174</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0698088483715</v>
+        <v>159.0441496485513</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.1274296111388</v>
+        <v>159.1004972766883</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9321553679468</v>
+        <v>158.9224191815678</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.6957674801799</v>
+        <v>158.703460240925</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.4665676074175</v>
+        <v>158.494170031915</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.8031883988871</v>
+        <v>158.8444297029191</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.1500769339969</v>
+        <v>159.2033378561006</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.6163816760279</v>
+        <v>159.6787221827305</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.767239794447</v>
+        <v>157.962733801858</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>156.8041948516477</v>
+        <v>157.128529297299</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.2824579488756</v>
+        <v>159.5759773239811</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>159.641368141168</v>
+        <v>160.0938287878763</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>161.888555641168</v>
+        <v>163.6224588588365</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2956065462247</v>
+        <v>139.2949829391877</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4593993104129</v>
+        <v>142.4584855237221</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7372899031585</v>
+        <v>143.7362974508909</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4151254981757</v>
+        <v>144.4141032846382</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3412324279917</v>
+        <v>144.3401929906036</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.262681957354</v>
+        <v>144.2616280552844</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2190090232445</v>
+        <v>144.2179494052516</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2584595688052</v>
+        <v>144.257401857968</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.928434152707</v>
+        <v>144.9273707686952</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.03722657516</v>
+        <v>148.0372429033115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316237332169</v>
+        <v>148.4316272502937</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535449960316</v>
+        <v>148.8535451410078</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9250232892729</v>
+        <v>148.9251437580537</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295254308169</v>
+        <v>149.295293547816</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4034108255757</v>
+        <v>150.4032478442001</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8501433866436</v>
+        <v>151.8497087949938</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.238387390752</v>
+        <v>152.2379242106613</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5686205350662</v>
+        <v>152.5681707474928</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1719904575597</v>
+        <v>153.1717031437315</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4073343581107</v>
+        <v>152.4072640887643</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8929961231383</v>
+        <v>152.8923191609265</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6690696419136</v>
+        <v>152.6681337875147</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6827779950231</v>
+        <v>152.6815433530972</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3648021206403</v>
+        <v>154.3632994534663</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3220730191034</v>
+        <v>155.3205694889196</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3079948043785</v>
+        <v>156.3063446610553</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9598316507133</v>
+        <v>157.9580102099097</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5811321762869</v>
+        <v>159.5795787850816</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4321097356958</v>
+        <v>161.4310773037491</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9162477920906</v>
+        <v>159.9167617235956</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6292863740798</v>
+        <v>159.6295235255374</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2508678964255</v>
+        <v>159.2525572635348</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5130661716358</v>
+        <v>157.5152789244986</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0388247299012</v>
+        <v>158.0409600765859</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3485195853218</v>
+        <v>158.3505025469375</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3975884143846</v>
+        <v>158.3996310699929</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6336627500769</v>
+        <v>159.6356044851088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4520056022824</v>
+        <v>158.4528848686004</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7036523003736</v>
+        <v>155.7029708750265</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8467384985716</v>
+        <v>155.8460120869482</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6562027801758</v>
+        <v>156.6559344668131</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2646380402765</v>
+        <v>156.2627464934343</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0286375623827</v>
+        <v>156.0266260709283</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.858341857223</v>
+        <v>155.8561184059974</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1362385385345</v>
+        <v>157.1349087651544</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6660187693344</v>
+        <v>158.666372881402</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1660549092541</v>
+        <v>159.1666226361501</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7630499234799</v>
+        <v>159.7638240354473</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6102827795196</v>
+        <v>159.6104383129888</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1861470904266</v>
+        <v>160.186401534187</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0416467206354</v>
+        <v>160.0411605726489</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8129303144389</v>
+        <v>159.8119636273709</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2966899058135</v>
+        <v>160.295870623841</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.998313182511</v>
+        <v>160.9970805659945</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6497170821581</v>
+        <v>161.6479652832708</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5135617918</v>
+        <v>161.5122821831966</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5190862474127</v>
+        <v>160.5195757944414</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.095496841335</v>
+        <v>160.0965988005071</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9220837380233</v>
+        <v>159.9236532542054</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.945435843429</v>
+        <v>159.9473501904706</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6452853658647</v>
+        <v>159.6489116211825</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8390854123127</v>
+        <v>158.8455891003318</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7696040661846</v>
+        <v>158.7770745346385</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7873107691646</v>
+        <v>158.7945452028131</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.8781927754174</v>
+        <v>158.8557018644501</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0441496485513</v>
+        <v>159.0192678222197</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.1004972766883</v>
+        <v>159.0736675476717</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9224191815678</v>
+        <v>158.9119358460347</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.703460240925</v>
+        <v>158.7100875320133</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.494170031915</v>
+        <v>158.5199335325013</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.8444297029191</v>
+        <v>158.8830536093235</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.2033378561006</v>
+        <v>159.253079510558</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.6787221827305</v>
+        <v>159.7365021584902</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.962733801858</v>
+        <v>158.1428761497832</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.128529297299</v>
+        <v>157.4204141700188</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.5759773239811</v>
+        <v>159.828955644651</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>160.0938287878763</v>
+        <v>160.4541085196828</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.6224588588365</v>
+        <v>163.6213401444134</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2949829391877</v>
+        <v>139.2943700831901</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4584855237221</v>
+        <v>142.4575874506902</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7362974508909</v>
+        <v>143.73532200304</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4141032846382</v>
+        <v>144.4130985218696</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3401929906036</v>
+        <v>144.3391713021496</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2616280552844</v>
+        <v>144.2605921530492</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2179494052516</v>
+        <v>144.2169078866656</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.257401857968</v>
+        <v>144.2563622141909</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9273707686952</v>
+        <v>144.9263254821374</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0372429033115</v>
+        <v>148.0372589463062</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316272502937</v>
+        <v>148.4316307043061</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535451410078</v>
+        <v>148.8535452812811</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9251437580537</v>
+        <v>148.9252621262649</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295293547816</v>
+        <v>149.2953321387502</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4032478442001</v>
+        <v>150.4030876938289</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8497087949938</v>
+        <v>151.8492816380895</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2379242106613</v>
+        <v>152.2374689383465</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5681707474928</v>
+        <v>152.5677286002516</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1717031437315</v>
+        <v>153.1714207007681</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4072640887643</v>
+        <v>152.4071950364654</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8923191609265</v>
+        <v>152.8916540007622</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6681337875147</v>
+        <v>152.667214178121</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6815433530972</v>
+        <v>152.6803299653412</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3632994534663</v>
+        <v>154.3618225863268</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3205694889196</v>
+        <v>155.3190916335799</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3063446610553</v>
+        <v>156.3047225924749</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9580102099097</v>
+        <v>157.9562195790983</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5795787850816</v>
+        <v>159.5780512311796</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4310773037491</v>
+        <v>161.4300617329635</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9167617235956</v>
+        <v>159.9172658826445</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6295235255374</v>
+        <v>159.6297558285588</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2525572635348</v>
+        <v>159.2542169137881</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5152789244986</v>
+        <v>157.5174531222171</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0409600765859</v>
+        <v>158.0430585029889</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3505025469375</v>
+        <v>158.3524515658833</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3996310699929</v>
+        <v>158.4016398130956</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6356044851088</v>
+        <v>159.637514298964</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4528848686004</v>
+        <v>158.4537503404913</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7029708750265</v>
+        <v>155.7023016868378</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8460120869482</v>
+        <v>155.8452987455696</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6559344668131</v>
+        <v>156.6556714923068</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2627464934343</v>
+        <v>156.2608870988571</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0266260709283</v>
+        <v>156.0246485269722</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8561184059974</v>
+        <v>155.8539318646355</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1349087651544</v>
+        <v>157.1336008885272</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.666372881402</v>
+        <v>158.6667212354075</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1666226361501</v>
+        <v>159.1671812029134</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7638240354473</v>
+        <v>159.7645857045331</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6104383129888</v>
+        <v>159.6105916729673</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.186401534187</v>
+        <v>160.1866524182618</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0411605726489</v>
+        <v>160.040683187129</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8119636273709</v>
+        <v>159.8110135096091</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.295870623841</v>
+        <v>160.2950654144393</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.9970805659945</v>
+        <v>160.9958688151819</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6479652832708</v>
+        <v>161.646243070403</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5122821831966</v>
+        <v>161.511022884425</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5195757944414</v>
+        <v>160.5200535495224</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0965988005071</v>
+        <v>160.0976794209139</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9236532542054</v>
+        <v>159.925194459835</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9473501904706</v>
+        <v>159.9492328005913</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6489116211825</v>
+        <v>159.6524774159974</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8455891003318</v>
+        <v>158.8519828885385</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7770745346385</v>
+        <v>158.784423676005</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.7945452028131</v>
+        <v>158.8016689282681</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.8557018644501</v>
+        <v>158.8388208359721</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0192678222197</v>
+        <v>159.0007355633778</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.0736675476717</v>
+        <v>159.053540506126</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9119358460347</v>
+        <v>158.9091739240887</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7100875320133</v>
+        <v>158.7254335748504</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.5199335325013</v>
+        <v>158.5553340860595</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.8830536093235</v>
+        <v>158.9330186996843</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.253079510558</v>
+        <v>159.3163062261639</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.7365021584902</v>
+        <v>159.8107071421397</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>158.1428761497832</v>
+        <v>158.337155816965</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.4204141700188</v>
+        <v>157.7220117078776</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.828955644651</v>
+        <v>160.1025687651751</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>160.4541085196828</v>
+        <v>160.8276803483519</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.6213401444134</v>
+        <v>163.8001501261905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2943700831901</v>
+        <v>139.2937677025915</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4575874506902</v>
+        <v>142.4567046894717</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.73532200304</v>
+        <v>143.734363126343</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4130985218696</v>
+        <v>144.4121107668695</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3391713021496</v>
+        <v>144.3381669119544</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2605921530492</v>
+        <v>144.2595737935019</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2169078866656</v>
+        <v>144.215884007761</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2563622141909</v>
+        <v>144.2553401785642</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9263254821374</v>
+        <v>144.9252978350672</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0372589463062</v>
+        <v>148.0372747115466</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316307043061</v>
+        <v>148.4316340969318</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535452812811</v>
+        <v>148.853545417027</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9252621262649</v>
+        <v>148.9253784483564</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2953321387502</v>
+        <v>149.2953700968778</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4030876938289</v>
+        <v>150.4029303013687</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8492816380895</v>
+        <v>151.8488617268328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2374689383465</v>
+        <v>152.2370213730902</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5677286002516</v>
+        <v>152.5672939004187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1714207007681</v>
+        <v>153.1711430059042</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4071950364654</v>
+        <v>152.4071271698655</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8916540007622</v>
+        <v>152.8910003368504</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.667214178121</v>
+        <v>152.66631039469</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6803299653412</v>
+        <v>152.6791372879571</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3618225863268</v>
+        <v>154.3603708609119</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3190916335799</v>
+        <v>155.3176388016753</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3047225924749</v>
+        <v>156.3031278891233</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9562195790983</v>
+        <v>157.9544589843993</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5780512311796</v>
+        <v>159.5765488771843</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4300617329635</v>
+        <v>161.4290626152074</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9172658826445</v>
+        <v>159.9177605426842</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6297558285588</v>
+        <v>159.6299834266067</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2542169137881</v>
+        <v>159.2558476232978</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5174531222171</v>
+        <v>157.5195897624654</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0430585029889</v>
+        <v>158.0451209569174</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3524515658833</v>
+        <v>158.3543675044751</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.4016398130956</v>
+        <v>158.4036154791928</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.637514298964</v>
+        <v>159.6393929697652</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4537503404913</v>
+        <v>158.4546023367238</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7023016868378</v>
+        <v>155.7016444099023</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8452987455696</v>
+        <v>155.8445981258313</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6556714923068</v>
+        <v>156.6554137020618</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2608870988571</v>
+        <v>156.2590590447239</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0246485269722</v>
+        <v>156.0227040797814</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8539318646355</v>
+        <v>155.8517813235786</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1336008885272</v>
+        <v>157.132314373468</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6667212354075</v>
+        <v>158.6670639700838</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1671812029134</v>
+        <v>159.1677308284217</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7645857045331</v>
+        <v>159.7653352266836</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6105916729673</v>
+        <v>159.6107429022952</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1866524182618</v>
+        <v>160.1868998131902</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.040683187129</v>
+        <v>160.0402143303367</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8110135096091</v>
+        <v>159.8100795393349</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2950654144393</v>
+        <v>160.2942739187718</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.9958688151819</v>
+        <v>160.9946774061189</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.646243070403</v>
+        <v>161.644549702887</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.511022884425</v>
+        <v>161.5097834220342</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5200535495224</v>
+        <v>160.5205198976706</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0976794209139</v>
+        <v>160.0987393004707</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.925194459835</v>
+        <v>159.9267080995073</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9492328005913</v>
+        <v>159.9510844395219</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6524774159974</v>
+        <v>159.6559842256347</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8519828885385</v>
+        <v>158.8582694940819</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.784423676005</v>
+        <v>158.7916543546735</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8016689282681</v>
+        <v>158.8086843783971</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.8388208359721</v>
+        <v>158.8224353782958</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>159.0007355633778</v>
+        <v>158.9828304232206</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.053540506126</v>
+        <v>159.0341657017251</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9091739240887</v>
+        <v>158.9064714348711</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7254335748504</v>
+        <v>158.7400943568036</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.5553340860595</v>
+        <v>158.5890732328294</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.9330186996843</v>
+        <v>158.9803138884664</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.3163062261639</v>
+        <v>159.3757575834803</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.8107071421397</v>
+        <v>159.8798701594053</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>158.337155816965</v>
+        <v>158.5170476496212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.7220117078776</v>
+        <v>157.9957283390517</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>160.1025687651751</v>
+        <v>160.3422932357467</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>160.8276803483519</v>
+        <v>161.1368628374569</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.8001501261905</v>
+        <v>163.9167362927388</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2937677025915</v>
+        <v>139.2931755310941</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4567046894717</v>
+        <v>142.4558368518067</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.734363126343</v>
+        <v>143.7334204021307</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4121107668695</v>
+        <v>144.4111395915031</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3381669119544</v>
+        <v>144.3371793844693</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2595737935019</v>
+        <v>144.2585725348436</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.215884007761</v>
+        <v>144.2148773242482</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2553401785642</v>
+        <v>144.2543353075865</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9252978350672</v>
+        <v>144.9242873848364</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0372747115466</v>
+        <v>148.037290206181</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316340969318</v>
+        <v>148.4316374297892</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853545417027</v>
+        <v>148.8535455484132</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9253784483564</v>
+        <v>148.9254927769131</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2953700968778</v>
+        <v>149.295407437591</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4029303013687</v>
+        <v>150.4027755962196</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8488617268328</v>
+        <v>151.8484488784826</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2370213730902</v>
+        <v>152.2365813209084</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5672939004187</v>
+        <v>152.5668664615077</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1711430059042</v>
+        <v>153.1708699404637</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4071271698655</v>
+        <v>152.4070604586835</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8910003368504</v>
+        <v>152.8903578738643</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.66631039469</v>
+        <v>152.6654220324587</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6791372879571</v>
+        <v>152.6779647955295</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3603708609119</v>
+        <v>154.3589436411024</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3176388016753</v>
+        <v>155.3162103636256</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3031278891233</v>
+        <v>156.301559865164</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9544589843993</v>
+        <v>157.9527276775911</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5765488771843</v>
+        <v>159.5750711064278</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4290626152074</v>
+        <v>161.4280795553602</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9177605426842</v>
+        <v>159.918245967135</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6299834266067</v>
+        <v>159.6302064576437</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2558476232978</v>
+        <v>159.2574501414211</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5195897624654</v>
+        <v>157.5216898088335</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0451209569174</v>
+        <v>158.0471483540621</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3543675044751</v>
+        <v>158.3562511961251</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.4036154791928</v>
+        <v>158.4055588766343</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6393929697652</v>
+        <v>159.6412412506384</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4546023367238</v>
+        <v>158.4554411664406</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7016444099023</v>
+        <v>155.7009987297602</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8445981258313</v>
+        <v>155.8439098913847</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6554137020618</v>
+        <v>156.6551609473037</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2590590447239</v>
+        <v>156.257261546281</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0227040797814</v>
+        <v>156.0207919067645</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8517813235786</v>
+        <v>155.849665902844</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.132314373468</v>
+        <v>157.131048702049</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6670639700838</v>
+        <v>158.6674012197626</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1677308284217</v>
+        <v>159.1682717246708</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7653352266836</v>
+        <v>159.7660728885923</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6107429022952</v>
+        <v>159.6108920427918</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1868998131902</v>
+        <v>160.187143787806</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0402143303367</v>
+        <v>160.0397537767397</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8100795393349</v>
+        <v>159.8091613089081</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2942739187718</v>
+        <v>160.2934957900771</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.9946774061189</v>
+        <v>160.993505832201</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.644549702887</v>
+        <v>161.6428844644875</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5097834220342</v>
+        <v>161.5085633369489</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5205198976706</v>
+        <v>160.5209752081793</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0987393004707</v>
+        <v>160.0997790154267</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9267080995073</v>
+        <v>159.9281948923882</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.9510844395219</v>
+        <v>159.952905849136</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6559842256347</v>
+        <v>159.6594334785883</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8582694940819</v>
+        <v>158.8644515467101</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7916543546735</v>
+        <v>158.7987693478233</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.8086843783971</v>
+        <v>158.815593918442</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.8224353782958</v>
+        <v>158.8293431452279</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.9828304232206</v>
+        <v>158.974042604698</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.0341657017251</v>
+        <v>159.0355641697215</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9064714348711</v>
+        <v>158.9145425330725</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.7400943568036</v>
+        <v>158.767960193386</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.5890732328294</v>
+        <v>158.6495522692215</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.9803138884664</v>
+        <v>159.0644304664754</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.3757575834803</v>
+        <v>159.4842803970055</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>159.8798701594053</v>
+        <v>160.0137919552152</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>158.5170476496212</v>
+        <v>158.7515932267572</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.9957283390517</v>
+        <v>158.3733494695666</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>160.3422932357467</v>
+        <v>160.7288202497916</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>161.1368628374569</v>
+        <v>161.648665594718</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.9167362927388</v>
+        <v>164.4796842123121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>166.7268717123121</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2931755310941</v>
+        <v>139.3811016470931</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4558368518067</v>
+        <v>142.5842831004387</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7334204021307</v>
+        <v>143.8723170767055</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4111395915031</v>
+        <v>144.5535801320392</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3371793844693</v>
+        <v>144.4820600199356</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2585725348436</v>
+        <v>144.4055072335612</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2148773242482</v>
+        <v>144.3626278799402</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2543353075865</v>
+        <v>144.4018222061611</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9242873848364</v>
+        <v>145.0719157542377</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037290206181</v>
+        <v>148.034953243022</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316374297892</v>
+        <v>148.4311184907811</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535455484132</v>
+        <v>148.853504259385</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9254927769131</v>
+        <v>148.9082807568449</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295407437591</v>
+        <v>149.2901537118013</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4027755962196</v>
+        <v>150.4259477283504</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8484488784826</v>
+        <v>151.909140249465</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2365813209084</v>
+        <v>152.3011093279179</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5668664615077</v>
+        <v>152.6291481753305</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1708699404637</v>
+        <v>153.2105702574121</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4070604586835</v>
+        <v>152.4170238596759</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8903578738643</v>
+        <v>152.9870196516481</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6654220324587</v>
+        <v>152.7983199858724</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6779647955295</v>
+        <v>152.8515840172256</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3589436411024</v>
+        <v>154.5695646486095</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3162103636256</v>
+        <v>155.5255337369924</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.301559865164</v>
+        <v>156.5302341719928</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9527276775911</v>
+        <v>158.2033395056165</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5750711064278</v>
+        <v>159.7844607625855</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4280795553602</v>
+        <v>161.5644058802658</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.918245967135</v>
+        <v>159.8370831831147</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6302064576437</v>
+        <v>159.5894819745992</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2574501414211</v>
+        <v>159.0139116241976</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5216898088335</v>
+        <v>157.2063097916022</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0471483540621</v>
+        <v>157.745742104927</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3562511961251</v>
+        <v>158.0798368057431</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.4055588766343</v>
+        <v>158.1305769695845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6412412506384</v>
+        <v>159.3828866555414</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4554411664406</v>
+        <v>158.3447858315276</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7009987297602</v>
+        <v>155.801684642553</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8439098913847</v>
+        <v>155.9514368154411</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6551609473037</v>
+        <v>156.699706476642</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.257261546281</v>
+        <v>156.5191159862578</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0207919067645</v>
+        <v>156.29683201208</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.849665902844</v>
+        <v>156.1491017180109</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.131048702049</v>
+        <v>157.3085449495575</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6674012197626</v>
+        <v>158.6208700464864</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1682717246708</v>
+        <v>159.0943142263096</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7660728885923</v>
+        <v>159.6657246220954</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6108920427918</v>
+        <v>159.5412962206535</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.187143787806</v>
+        <v>160.0216197576559</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0397537767397</v>
+        <v>159.7834240825533</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8091613089081</v>
+        <v>159.5459131804057</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2934957900771</v>
+        <v>159.9014898286269</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.993505832201</v>
+        <v>160.0372326820399</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.6428844644875</v>
+        <v>160.1300124744793</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.5085633369489</v>
+        <v>159.9488998847016</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5209752081793</v>
+        <v>159.6540466899668</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.0997790154267</v>
+        <v>159.5384939949332</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.9281948923882</v>
+        <v>159.720332405347</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>159.952905849136</v>
+        <v>160.8589742447758</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>159.6594334785883</v>
+        <v>160.8749539956557</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>158.8644515467101</v>
+        <v>161.2115980773244</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>158.7987693478233</v>
+        <v>162.6334475755227</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>158.815593918442</v>
+        <v>157.4551464169446</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>158.8293431452279</v>
+        <v>157.5713197090784</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.974042604698</v>
+        <v>157.8275704886825</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>159.0355641697215</v>
+        <v>157.9284983034036</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.9145425330725</v>
+        <v>158.3999432199309</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.767960193386</v>
+        <v>158.860304941501</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.6495522692215</v>
+        <v>159.3340257603849</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.0644304664754</v>
+        <v>159.9853194713556</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>159.4842803970055</v>
+        <v>160.5133302480563</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>160.0137919552152</v>
+        <v>161.1035431896017</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>158.7515932267572</v>
+        <v>161.8301968957997</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>158.3733494695666</v>
+        <v>162.2314586580271</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>160.7288202497916</v>
+        <v>162.4837167057658</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>161.648665594718</v>
+        <v>162.3054777034536</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>164.4796842123121</v>
+        <v>164.5408588617231</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>166.7268717123121</v>
+        <v>166.7880463617231</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3811016470931</v>
+        <v>139.3781360645118</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5842831004387</v>
+        <v>142.5799644893485</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8723170767055</v>
+        <v>143.8676681203606</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5535801320392</v>
+        <v>144.5488341157157</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4820600199356</v>
+        <v>144.4772313159458</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4055072335612</v>
+        <v>144.4006087575585</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3626278799402</v>
+        <v>144.3577015484811</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.4018222061611</v>
+        <v>144.3969045855854</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0719157542377</v>
+        <v>145.067016017164</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.034953243022</v>
+        <v>148.0350332301677</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311184907811</v>
+        <v>148.4311367652115</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.853504259385</v>
+        <v>148.8535063483358</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9082807568449</v>
+        <v>148.9088689242981</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2901537118013</v>
+        <v>149.2903210723669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4259477283504</v>
+        <v>150.4251600166228</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.909140249465</v>
+        <v>151.9071140209406</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.3011093279179</v>
+        <v>152.2989603883208</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6291481753305</v>
+        <v>152.6270873403017</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2105702574121</v>
+        <v>153.2092592439593</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4170238596759</v>
+        <v>152.4166858656288</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9870196516481</v>
+        <v>152.9837198717024</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7983199858724</v>
+        <v>152.7938093392563</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8515840172256</v>
+        <v>152.8457489161418</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5695646486095</v>
+        <v>154.5625104506074</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5255337369924</v>
+        <v>155.5185736971024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5302341719928</v>
+        <v>156.5226691371809</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.2033395056165</v>
+        <v>158.1951133180679</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7844607625855</v>
+        <v>159.7777424387998</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5644058802658</v>
+        <v>161.5601280528322</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8370831831147</v>
+        <v>159.8401129934515</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5894819745992</v>
+        <v>159.5911016532715</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0139116241976</v>
+        <v>159.0222955931374</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2063097916022</v>
+        <v>157.2170449804041</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.745742104927</v>
+        <v>157.7558968844085</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0798368057431</v>
+        <v>158.0890256821633</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1305769695845</v>
+        <v>158.1393946764714</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3828866555414</v>
+        <v>159.3910631770347</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3447858315276</v>
+        <v>158.3480608033365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.801684642553</v>
+        <v>155.7981358880978</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9514368154411</v>
+        <v>155.9476422607791</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.699706476642</v>
+        <v>156.6979812424232</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5191159862578</v>
+        <v>156.5104622382865</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.29683201208</v>
+        <v>156.287795380466</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1491017180109</v>
+        <v>156.1394906839529</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.3085449495575</v>
+        <v>157.302900171725</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6208700464864</v>
+        <v>158.6223224461958</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0943142263096</v>
+        <v>159.0966007123477</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6657246220954</v>
+        <v>159.6688076880049</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5412962206535</v>
+        <v>159.5420313807832</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0216197576559</v>
+        <v>160.023225340968</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.7834240825533</v>
+        <v>159.7821134485265</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.5459131804057</v>
+        <v>159.5422769496143</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.9014898286269</v>
+        <v>159.8987433661966</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0372326820399</v>
+        <v>160.0343097780669</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1300124744793</v>
+        <v>160.1270872226218</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9488998847016</v>
+        <v>159.9465125047359</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.6540466899668</v>
+        <v>159.6519580581341</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.5384939949332</v>
+        <v>159.5371480219761</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.720332405347</v>
+        <v>159.7198285605909</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.8589742447758</v>
+        <v>160.8581422813548</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8749539956557</v>
+        <v>160.8737688177617</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2115980773244</v>
+        <v>161.2101900620457</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.6334475755227</v>
+        <v>162.6321425757021</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>157.4551464169446</v>
+        <v>157.4552290338223</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>157.5713197090784</v>
+        <v>157.5709466789978</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>157.8275704886825</v>
+        <v>157.8748574744943</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>157.9284983034036</v>
+        <v>158.0203224188464</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.3999432199309</v>
+        <v>158.462546084029</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.860304941501</v>
+        <v>158.9763367944194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.3340257603849</v>
+        <v>159.4940304474111</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>159.9853194713556</v>
+        <v>160.174613348723</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>160.5133302480563</v>
+        <v>160.7341401136189</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.1035431896017</v>
+        <v>161.3446828217046</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>161.8301968957997</v>
+        <v>162.0662251100605</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>162.2314586580271</v>
+        <v>162.5564011723635</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>162.4837167057658</v>
+        <v>162.8638630773681</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>162.3054777034536</v>
+        <v>162.7792167818851</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>164.5408588617231</v>
+        <v>164.9103626229215</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>166.7880463617231</v>
+        <v>167.1575501229215</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3781360645118</v>
+        <v>139.2982143483456</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5799644893485</v>
+        <v>142.4632201406353</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8676681203606</v>
+        <v>143.7414389693106</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5488341157157</v>
+        <v>144.4193982777528</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4772313159458</v>
+        <v>144.345577247933</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.4006087575585</v>
+        <v>144.2670872827312</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3577015484811</v>
+        <v>144.2234382629343</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3969045855854</v>
+        <v>144.262880839073</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.067016017164</v>
+        <v>144.9328783972039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0350332301677</v>
+        <v>148.037158253398</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311367652115</v>
+        <v>148.4316089985016</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535063483358</v>
+        <v>148.8535443652936</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9088689242981</v>
+        <v>148.9245192493669</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2903210723669</v>
+        <v>149.295090525093</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4251600166228</v>
+        <v>150.4040926166575</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9071140209406</v>
+        <v>151.8519601211629</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2989603883208</v>
+        <v>152.2403234558214</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6270873403017</v>
+        <v>152.5705001885672</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2092592439593</v>
+        <v>153.1731910301594</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4166858656288</v>
+        <v>152.4076282730373</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9837198717024</v>
+        <v>152.895828501659</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7938093392563</v>
+        <v>152.6729844267196</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8457489161418</v>
+        <v>152.6879406703937</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5625104506074</v>
+        <v>154.3710847886761</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5185736971024</v>
+        <v>155.32835773529</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5226691371809</v>
+        <v>156.3148912032648</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1951133180679</v>
+        <v>157.9674419531432</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7777424387998</v>
+        <v>159.587617637867</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5601280528322</v>
+        <v>161.4364167239829</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8401129934515</v>
+        <v>159.9140884940674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5911016532715</v>
+        <v>159.6282862064067</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0222955931374</v>
+        <v>159.2437967315097</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2170449804041</v>
+        <v>157.5038083749405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7558968844085</v>
+        <v>158.0298939785429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.0890256821633</v>
+        <v>158.3402299816732</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1393946764714</v>
+        <v>158.3890609407858</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.3910631770347</v>
+        <v>159.6255601010777</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3480608033365</v>
+        <v>158.4483438591864</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7981358880978</v>
+        <v>155.706507322213</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9476422607791</v>
+        <v>155.8497822808783</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6979812424232</v>
+        <v>156.6573327341726</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.5104622382865</v>
+        <v>156.2725430016439</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.287795380466</v>
+        <v>156.0370410724192</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1394906839529</v>
+        <v>155.8676240588798</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.302900171725</v>
+        <v>157.141787948829</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6223224461958</v>
+        <v>158.6645418013738</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.0966007123477</v>
+        <v>159.1636877658732</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6688076880049</v>
+        <v>159.7598227825914</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5420313807832</v>
+        <v>159.609638016775</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.023225340968</v>
+        <v>160.1850922455459</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.7821134485265</v>
+        <v>160.043683920873</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.5422769496143</v>
+        <v>159.8169717241156</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.8987433661966</v>
+        <v>160.3001153892157</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0343097780669</v>
+        <v>161.0034634348467</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1270872226218</v>
+        <v>161.447281642821</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9465125047359</v>
+        <v>161.407648494496</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.6519580581341</v>
+        <v>160.5244928382508</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.5371480219761</v>
+        <v>160.1605236322262</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.7198285605909</v>
+        <v>160.0044891408575</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.8581422813548</v>
+        <v>160.055806803399</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8737688177617</v>
+        <v>160.011273615219</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2101900620457</v>
+        <v>159.2987968977682</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.6321425757021</v>
+        <v>159.1964421063029</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>157.4552290338223</v>
+        <v>159.0996057592579</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>157.5709466789978</v>
+        <v>159.0148878037081</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>157.8748574744943</v>
+        <v>158.963136276403</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.0203224188464</v>
+        <v>158.6730605235641</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.462546084029</v>
+        <v>158.3319157662197</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.9763367944194</v>
+        <v>158.2962758895046</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.4940304474111</v>
+        <v>158.0496185039803</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.174613348723</v>
+        <v>158.4991987237349</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>160.7341401136189</v>
+        <v>158.4209502786176</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.3446828217046</v>
+        <v>158.5539400661501</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.0662251100605</v>
+        <v>157.3408972411069</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>162.5564011723635</v>
+        <v>156.6929881096476</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>162.8638630773681</v>
+        <v>158.7730674494391</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>162.7792167818851</v>
+        <v>160.9026239171984</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>164.9103626229215</v>
+        <v>163.9262057537762</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>167.1575501229215</v>
+        <v>168.0389757409615</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2982143483456</v>
+        <v>139.3725283071106</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4632201406353</v>
+        <v>142.5717955976276</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7414389693106</v>
+        <v>143.8588703087217</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4193982777528</v>
+        <v>144.5398484583554</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.345577247933</v>
+        <v>144.4680893728877</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2670872827312</v>
+        <v>144.3913349718661</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2234382629343</v>
+        <v>144.3483751537432</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.262880839073</v>
+        <v>144.387594697752</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9328783972039</v>
+        <v>145.0577356045175</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.037158253398</v>
+        <v>148.0351842637225</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316089985016</v>
+        <v>148.4311711772421</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535443652936</v>
+        <v>148.8535101688488</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9245192493669</v>
+        <v>148.9099796815174</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295090525093</v>
+        <v>149.290639472834</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4040926166575</v>
+        <v>150.4236715903073</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8519601211629</v>
+        <v>151.903278424376</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2403234558214</v>
+        <v>152.2948914688011</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5705001885672</v>
+        <v>152.6231826535978</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1731910301594</v>
+        <v>153.2067747954434</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4076282730373</v>
+        <v>152.4160471156285</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.895828501659</v>
+        <v>152.9774873393454</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6729844267196</v>
+        <v>152.7852845566735</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6879406703937</v>
+        <v>152.8347101654888</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3710847886761</v>
+        <v>154.5491605910134</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.32835773529</v>
+        <v>155.5053919494767</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3148912032648</v>
+        <v>156.5083338418313</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9674419531432</v>
+        <v>158.1795122780967</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.587617637867</v>
+        <v>159.7649702988231</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4364167239829</v>
+        <v>161.5519771990404</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9140884940674</v>
+        <v>159.8457875552255</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6282862064067</v>
+        <v>159.5941181303548</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2437967315097</v>
+        <v>159.0381193170138</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5038083749405</v>
+        <v>157.2373293635169</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0298939785429</v>
+        <v>157.7751053353056</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3402299816732</v>
+        <v>158.1064316139812</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3890609407858</v>
+        <v>158.1561575788822</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6255601010777</v>
+        <v>159.406628588951</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4483438591864</v>
+        <v>158.3543408977798</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.706507322213</v>
+        <v>155.7914535485272</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8497822808783</v>
+        <v>155.9404976172052</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6573327341726</v>
+        <v>156.6947600278785</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2725430016439</v>
+        <v>156.4940622764708</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0370410724192</v>
+        <v>156.2706527986764</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8676240588798</v>
+        <v>156.1212224250886</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.141787948829</v>
+        <v>157.2921611745616</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6645418013738</v>
+        <v>158.6250912715631</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1636877658732</v>
+        <v>159.1009638396498</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7598227825914</v>
+        <v>159.6746950437098</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.609638016775</v>
+        <v>159.5434516242734</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1850922455459</v>
+        <v>160.0263062986414</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.043683920873</v>
+        <v>159.7796573169364</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8169717241156</v>
+        <v>159.5354005515316</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.3001153892157</v>
+        <v>159.8935565639056</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0034634348467</v>
+        <v>160.0287847623654</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.447281642821</v>
+        <v>160.121554480567</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.407648494496</v>
+        <v>159.9419961093295</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5244928382508</v>
+        <v>159.6480043984199</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1605236322262</v>
+        <v>159.534602197069</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0044891408575</v>
+        <v>159.7188791306045</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.055806803399</v>
+        <v>160.8565706070593</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.011273615219</v>
+        <v>160.8715285522177</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.2987968977682</v>
+        <v>161.2075286139233</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.1964421063029</v>
+        <v>162.6296748911234</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.0996057592579</v>
+        <v>157.4553852070338</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0148878037081</v>
+        <v>157.5702416090309</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.963136276403</v>
+        <v>157.9417911914922</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.6730605235641</v>
+        <v>158.1562674586105</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.3319157662197</v>
+        <v>158.5534423964243</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.2962758895046</v>
+        <v>159.1613726254485</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.0496185039803</v>
+        <v>159.7440563491595</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.4991987237349</v>
+        <v>160.4688488032847</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.4209502786176</v>
+        <v>161.0765242874542</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>158.5539400661501</v>
+        <v>161.7180770049946</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.3408972411069</v>
+        <v>162.432549657477</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>156.6929881096476</v>
+        <v>163.0598153857428</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>158.7730674494391</v>
+        <v>163.4519357499154</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>160.9026239171984</v>
+        <v>163.511445604651</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.9262057537762</v>
+        <v>165.4426423567198</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>168.0389757409615</v>
+        <v>167.8270377400305</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3725283071106</v>
+        <v>139.2975447789526</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5717955976276</v>
+        <v>142.4622391874844</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8588703087217</v>
+        <v>143.7403738517004</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5398484583554</v>
+        <v>144.4183015103029</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4680893728877</v>
+        <v>144.3444619815785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3913349718661</v>
+        <v>144.2659564786166</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3483751537432</v>
+        <v>144.2223013169091</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.387594697752</v>
+        <v>144.261745938333</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0577356045175</v>
+        <v>144.9317377131939</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0351842637225</v>
+        <v>148.0371758016897</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311711772421</v>
+        <v>148.4316127858852</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535101688488</v>
+        <v>148.8535445310061</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9099796815174</v>
+        <v>148.924648705249</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.290639472834</v>
+        <v>149.2951325297149</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4236715903073</v>
+        <v>150.4039175264422</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.903278424376</v>
+        <v>151.8514937623499</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2948914688011</v>
+        <v>152.2398264921461</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6231826535978</v>
+        <v>152.570017771563</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2067747954434</v>
+        <v>153.1728829170195</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4160471156285</v>
+        <v>152.4075527989486</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9774873393454</v>
+        <v>152.8951010470314</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7852845566735</v>
+        <v>152.6719790933324</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8347101654888</v>
+        <v>152.6866151768635</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5491605910134</v>
+        <v>154.3694718591886</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.5053919494767</v>
+        <v>155.3267445206177</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5083338418313</v>
+        <v>156.3131211551009</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1795122780967</v>
+        <v>157.9654889804128</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7649702988231</v>
+        <v>159.5859540773176</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5519771990404</v>
+        <v>161.4353124864661</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8457875552255</v>
+        <v>159.9146444677294</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5941181303548</v>
+        <v>159.628544306123</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0381193170138</v>
+        <v>159.245613305782</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2373293635169</v>
+        <v>157.5061860617091</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7751053353056</v>
+        <v>158.0321871780181</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1064316139812</v>
+        <v>158.3423579607772</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1561575788822</v>
+        <v>158.3912481857884</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.406628588951</v>
+        <v>159.6276378395223</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3543408977798</v>
+        <v>158.4492816967742</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7914535485272</v>
+        <v>155.7057734413073</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9404976172052</v>
+        <v>155.8489998367984</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6947600278785</v>
+        <v>156.6570413927372</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4940622764708</v>
+        <v>156.2705141437275</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2706527986764</v>
+        <v>156.034884677068</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1212224250886</v>
+        <v>155.8652432359956</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2921611745616</v>
+        <v>157.1403648653492</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6250912715631</v>
+        <v>158.6649204275562</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1009638396498</v>
+        <v>159.1642944697953</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6746950437098</v>
+        <v>159.7606498240619</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5434516242734</v>
+        <v>159.6098026939189</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0263062986414</v>
+        <v>160.185361669119</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.7796573169364</v>
+        <v>160.0431602079147</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.5354005515316</v>
+        <v>159.8159342356218</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.8935565639056</v>
+        <v>160.299235967964</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0287847623654</v>
+        <v>161.0021417420194</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.121554480567</v>
+        <v>161.4456440751898</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9419961093295</v>
+        <v>161.4063905923284</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.6480043984199</v>
+        <v>160.5248470853415</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.534602197069</v>
+        <v>160.1614390741068</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.7188791306045</v>
+        <v>160.0058547569656</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.8565706070593</v>
+        <v>160.0575455813718</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8715285522177</v>
+        <v>160.0142535098728</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2075286139233</v>
+        <v>159.3045184553677</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.6296748911234</v>
+        <v>159.203493597248</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>157.4553852070338</v>
+        <v>159.1066758046496</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>157.5702416090309</v>
+        <v>159.0223708856852</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>157.9417911914922</v>
+        <v>158.9539426537503</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.1562674586105</v>
+        <v>158.6871605819378</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.5534423964243</v>
+        <v>158.3587053451755</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.1613726254485</v>
+        <v>158.3498808223035</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.7440563491595</v>
+        <v>158.1309390240854</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.4688488032847</v>
+        <v>158.5997261709658</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.0765242874542</v>
+        <v>158.5582191297968</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.7180770049946</v>
+        <v>158.730743641811</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.432549657477</v>
+        <v>157.6186182568355</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>163.0598153857428</v>
+        <v>157.1042259571796</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>163.4519357499154</v>
+        <v>159.2007322327055</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>163.511445604651</v>
+        <v>161.3606753837471</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>165.4426423567198</v>
+        <v>164.3456990113762</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>167.8270377400305</v>
+        <v>168.18960472697</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2975447789526</v>
+        <v>139.3698745871107</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4622391874844</v>
+        <v>142.5679286922923</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7403738517004</v>
+        <v>143.854703845829</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4183015103029</v>
+        <v>144.5355911383277</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3444619815785</v>
+        <v>144.4637581279237</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2659564786166</v>
+        <v>144.386941378203</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2223013169091</v>
+        <v>144.3439566935362</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.261745938333</v>
+        <v>144.3831840649692</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9317377131939</v>
+        <v>145.0533369413542</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371758016897</v>
+        <v>148.0352556366437</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316127858852</v>
+        <v>148.4311873959585</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535445310061</v>
+        <v>148.8535119175007</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.924648705249</v>
+        <v>148.9105046612469</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2951325297149</v>
+        <v>149.2907910242423</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4039175264422</v>
+        <v>150.4229677369347</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8514937623499</v>
+        <v>151.9014614678548</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2398264921461</v>
+        <v>152.2929635137482</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.570017771563</v>
+        <v>152.6213313380855</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1728829170195</v>
+        <v>153.2055966411255</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4075527989486</v>
+        <v>152.4157450166318</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8951010470314</v>
+        <v>152.9745412574586</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6719790933324</v>
+        <v>152.7812525850595</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6866151768635</v>
+        <v>152.8294842048589</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3694718591886</v>
+        <v>154.5428383089382</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3267445206177</v>
+        <v>155.4991447105661</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3131211551009</v>
+        <v>156.5015363963679</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9654889804128</v>
+        <v>158.1721087971423</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5859540773176</v>
+        <v>159.7588953025947</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4353124864661</v>
+        <v>161.5480919197498</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9146444677294</v>
+        <v>159.8484478899777</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.628544306123</v>
+        <v>159.5955244560758</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.245613305782</v>
+        <v>159.0455936641646</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5061860617091</v>
+        <v>157.246921210045</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0321871780181</v>
+        <v>157.7841978243768</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3423579607772</v>
+        <v>158.1146820045218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3912481857884</v>
+        <v>158.1641306843555</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6276378395223</v>
+        <v>159.4140418628989</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4492816967742</v>
+        <v>158.3573526001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7057734413073</v>
+        <v>155.7883042228187</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8489998367984</v>
+        <v>155.937130679858</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6570413927372</v>
+        <v>156.6932545165316</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2705141437275</v>
+        <v>156.4862850707019</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.034884677068</v>
+        <v>156.2625157035659</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8652432359956</v>
+        <v>156.1125345191491</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1403648653492</v>
+        <v>157.2870495608553</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6649204275562</v>
+        <v>158.6264117621247</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1642944697953</v>
+        <v>159.103046602795</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7606498240619</v>
+        <v>159.6775072847548</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6098026939189</v>
+        <v>159.5441374477472</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.185361669119</v>
+        <v>160.0277847812358</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0431602079147</v>
+        <v>159.7785051987757</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8159342356218</v>
+        <v>159.5321463094255</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.299235967964</v>
+        <v>159.8911051086386</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0021417420194</v>
+        <v>160.02617116595</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.4456440751898</v>
+        <v>160.1189357202407</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4063905923284</v>
+        <v>159.9398579577933</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5248470853415</v>
+        <v>159.6461315403222</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1614390741068</v>
+        <v>159.5333971515816</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0058547569656</v>
+        <v>159.7184313478447</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0575455813718</v>
+        <v>160.8558275503329</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.0142535098728</v>
+        <v>160.8704687914991</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.3045184553677</v>
+        <v>161.2062696270732</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.203493597248</v>
+        <v>162.6285071259276</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.1066758046496</v>
+        <v>157.4554590885651</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0223708856852</v>
+        <v>157.5699080982682</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.9539426537503</v>
+        <v>157.9751965382253</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.6871605819378</v>
+        <v>158.2187763795645</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.3587053451755</v>
+        <v>158.5974922359921</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.3498808223035</v>
+        <v>159.244076966345</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.1309390240854</v>
+        <v>159.8531754714532</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.5997261709658</v>
+        <v>160.5965692974012</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.5582191297968</v>
+        <v>161.2246692348337</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>158.730743641811</v>
+        <v>161.8802137439143</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.6186182568355</v>
+        <v>162.5941284097963</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.1042259571796</v>
+        <v>163.2784750844616</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.2007322327055</v>
+        <v>163.7060677656555</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>161.3606753837471</v>
+        <v>163.8242299176767</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>164.3456990113762</v>
+        <v>165.6727981638845</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>168.18960472697</v>
+        <v>167.8896474597723</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.2187763795645</v>
+        <v>158.2195119623345</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.5974922359921</v>
+        <v>158.597632308188</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.244076966345</v>
+        <v>159.2531561053845</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.8531754714532</v>
+        <v>159.853599177275</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.5965692974012</v>
+        <v>160.596948480254</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.2246692348337</v>
+        <v>161.2250399425958</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.8802137439143</v>
+        <v>161.8805954869022</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.5941284097963</v>
+        <v>162.5945479439545</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>163.2784750844616</v>
+        <v>163.2790127522374</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>163.7060677656555</v>
+        <v>163.7066523479465</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>163.8242299176767</v>
+        <v>163.8248766674571</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>165.6727981638845</v>
+        <v>165.6737183880084</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>167.8896474597723</v>
+        <v>167.8917400897701</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3698745871107</v>
+        <v>139.2968871651942</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5679286922923</v>
+        <v>142.4612757037071</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.854703845829</v>
+        <v>143.7393276308444</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5355911383277</v>
+        <v>144.4172241278273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.4637581279237</v>
+        <v>144.3433664319168</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.386941378203</v>
+        <v>144.2648456703897</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3439566935362</v>
+        <v>144.2211844776249</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3831840649692</v>
+        <v>144.2606311084284</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0533369413542</v>
+        <v>144.9306171255971</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0352556366437</v>
+        <v>148.0371930324391</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4311873959585</v>
+        <v>148.4316165028498</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535119175007</v>
+        <v>148.8535446912275</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9105046612469</v>
+        <v>148.9247758223706</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2907910242423</v>
+        <v>149.2951738164097</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4229677369347</v>
+        <v>150.4037455868544</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.9014614678548</v>
+        <v>151.8510356640408</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2929635137482</v>
+        <v>152.239338312579</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6213313380855</v>
+        <v>152.5695438367867</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2055966411255</v>
+        <v>153.1725802103926</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4157450166318</v>
+        <v>152.4074786789654</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9745412574586</v>
+        <v>152.8943867320564</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7812525850595</v>
+        <v>152.6709918371379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8294842048589</v>
+        <v>152.6853133133952</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5428383089382</v>
+        <v>154.3678876051931</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4991447105661</v>
+        <v>155.3251598245541</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.5015363963679</v>
+        <v>156.3113822779254</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1721087971423</v>
+        <v>157.9635701928103</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.7588953025947</v>
+        <v>159.584319129135</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.5480919197498</v>
+        <v>161.4342268839084</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8484478899777</v>
+        <v>159.9151894648929</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5955244560758</v>
+        <v>159.6287969228526</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0455936641646</v>
+        <v>159.2473967661288</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.246921210045</v>
+        <v>157.5085208301662</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7841978243768</v>
+        <v>158.0344393152893</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1146820045218</v>
+        <v>158.3444482326613</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1641306843555</v>
+        <v>158.3933978809634</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4140418628989</v>
+        <v>159.6296802727138</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3573526001</v>
+        <v>158.4502043609164</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7883042228187</v>
+        <v>155.7050532265634</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.937130679858</v>
+        <v>155.8482319916475</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6932545165316</v>
+        <v>156.6567560726728</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4862850707019</v>
+        <v>156.2685209804886</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2625157035659</v>
+        <v>156.0327659387557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1125345191491</v>
+        <v>155.8629032829395</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2870495608553</v>
+        <v>157.1389660069574</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6264117621247</v>
+        <v>158.6652926929829</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.103046602795</v>
+        <v>159.1648910634522</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6775072847548</v>
+        <v>159.7614631385916</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5441374477472</v>
+        <v>159.6099650154917</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0277847812358</v>
+        <v>160.1856272328968</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.7785051987757</v>
+        <v>160.0426462822711</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.5321463094255</v>
+        <v>159.8149151584213</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.8911051086386</v>
+        <v>160.2983721863977</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.02617116595</v>
+        <v>161.0008431997373</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1189357202407</v>
+        <v>161.4440351351042</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9398579577933</v>
+        <v>161.405153280541</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.6461315403222</v>
+        <v>160.5251915085818</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.5333971515816</v>
+        <v>160.1623353560563</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.7184313478447</v>
+        <v>160.0071941708397</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.8558275503329</v>
+        <v>160.0592537051054</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8704687914991</v>
+        <v>160.0171810394615</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2062696270732</v>
+        <v>159.3101377809475</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.6285071259276</v>
+        <v>159.2104228379084</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>157.4554590885651</v>
+        <v>159.1136292872285</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>157.5699080982682</v>
+        <v>159.0297358741936</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>157.9751965382253</v>
+        <v>158.9611706005046</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.2195119623345</v>
+        <v>158.6783953948333</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.597632308188</v>
+        <v>158.3607249143071</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.2531561053845</v>
+        <v>158.3476089826934</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.853599177275</v>
+        <v>158.1497288927847</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.596948480254</v>
+        <v>158.6180814835569</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.2250399425958</v>
+        <v>158.5907080464819</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.8805954869022</v>
+        <v>158.7731092603531</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.5945479439545</v>
+        <v>157.7181892461539</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>163.2790127522374</v>
+        <v>157.2441563892025</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>163.7066523479465</v>
+        <v>159.2794380449415</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>163.8248766674571</v>
+        <v>161.3212751728899</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>165.6737183880084</v>
+        <v>164.0036284691061</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>167.8917400897701</v>
+        <v>166.9672485346526</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>164.7200610346526</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2968871651942</v>
+        <v>139.3673139509193</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4612757037071</v>
+        <v>142.5641966970222</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7393276308444</v>
+        <v>143.8506816213198</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4172241278273</v>
+        <v>144.5314800482421</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3433664319168</v>
+        <v>144.459575726146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.2648456703897</v>
+        <v>144.3826988405152</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2211844776249</v>
+        <v>144.3396901793822</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2606311084284</v>
+        <v>144.3789251133938</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.9306171255971</v>
+        <v>145.0490883350955</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0371930324391</v>
+        <v>148.0353244451802</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316165028498</v>
+        <v>148.4312030055462</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535446912275</v>
+        <v>148.8535135685736</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9247758223706</v>
+        <v>148.9110108259473</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2951738164097</v>
+        <v>149.2909377918153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4037455868544</v>
+        <v>150.4222888826206</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8510356640408</v>
+        <v>151.8997071144252</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.239338312579</v>
+        <v>152.2911016993117</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5695438367867</v>
+        <v>152.6195428180878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1725802103926</v>
+        <v>153.2044583185796</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4074786789654</v>
+        <v>152.4154536189139</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8943867320564</v>
+        <v>152.9717005361675</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6709918371379</v>
+        <v>152.7773633820941</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6853133133952</v>
+        <v>152.8244402674729</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3678876051931</v>
+        <v>154.5367349035052</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3251598245541</v>
+        <v>155.4931109801591</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3113822779254</v>
+        <v>156.4949691430095</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9635701928103</v>
+        <v>158.1649524869631</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.584319129135</v>
+        <v>159.753014653285</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4342268839084</v>
+        <v>161.544325825536</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9151894648929</v>
+        <v>159.8509996382289</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6287969228526</v>
+        <v>159.5968685477674</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2473967661288</v>
+        <v>159.0527973330267</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5085208301662</v>
+        <v>157.2561720963494</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0344393152893</v>
+        <v>157.7929728086198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3444482326613</v>
+        <v>158.1226510472318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3933978809634</v>
+        <v>158.1718487259662</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6296802727138</v>
+        <v>159.4212238971686</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4502043609164</v>
+        <v>158.3602829147946</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7050532265634</v>
+        <v>155.7852732680265</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8482319916475</v>
+        <v>155.9338904686024</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6567560726728</v>
+        <v>156.6918133437926</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2685209804886</v>
+        <v>156.4787707773145</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0327659387557</v>
+        <v>156.2546490020273</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.8629032829395</v>
+        <v>156.1041252389548</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1389660069574</v>
+        <v>157.2820991629691</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6652926929829</v>
+        <v>158.6276921555173</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1648910634522</v>
+        <v>159.1050672996292</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7614631385916</v>
+        <v>159.6802368506278</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6099650154917</v>
+        <v>159.5448075817803</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1856272328968</v>
+        <v>160.0292239094989</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0426462822711</v>
+        <v>159.7773997240638</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8149151584213</v>
+        <v>159.5290061383703</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2983721863977</v>
+        <v>159.888741531569</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>161.0008431997373</v>
+        <v>160.0236498583409</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.4440351351042</v>
+        <v>160.1164085064736</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.405153280541</v>
+        <v>159.9377942743288</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5251915085818</v>
+        <v>159.644323225198</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1623353560563</v>
+        <v>159.532234190653</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.0071941708397</v>
+        <v>159.7180001901735</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0592537051054</v>
+        <v>160.855110981848</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.0171810394615</v>
+        <v>160.8694464382091</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.3101377809475</v>
+        <v>161.2050550889949</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.2104228379084</v>
+        <v>162.6273803221112</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.1136292872285</v>
+        <v>157.4555303644058</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0297358741936</v>
+        <v>157.5695863759555</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.9611706005046</v>
+        <v>157.9745918000207</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.6783953948333</v>
+        <v>158.2117088684738</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.3607249143071</v>
+        <v>158.565631275755</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.3476089826934</v>
+        <v>159.1768060040584</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.1497288927847</v>
+        <v>159.7240471993246</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.6180814835569</v>
+        <v>160.4506580050188</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.5907080464819</v>
+        <v>161.0597756827065</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>158.7731092603531</v>
+        <v>161.6901158753492</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.7181892461539</v>
+        <v>162.3612655043751</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.2441563892025</v>
+        <v>162.9887903822166</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.2794380449415</v>
+        <v>163.4057437462531</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>161.3212751728899</v>
+        <v>163.5140564753324</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>164.0036284691061</v>
+        <v>165.1104287468766</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>166.9672485346526</v>
+        <v>166.4625126393049</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>164.7200610346526</v>
+        <v>164.2153251393049</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.3673139509193</v>
+        <v>139.2962411896976</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.5641966970222</v>
+        <v>142.4603292267925</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.8506816213198</v>
+        <v>143.7382998083404</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.5314800482421</v>
+        <v>144.4161656209991</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.459575726146</v>
+        <v>144.342290080779</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.3826988405152</v>
+        <v>144.2637543324245</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.3396901793822</v>
+        <v>144.2200872164818</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.3789251133938</v>
+        <v>144.259535821696</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>145.0490883350955</v>
+        <v>144.9295161081265</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.0353244451802</v>
+        <v>148.0372099541842</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4312030055462</v>
+        <v>148.4316201513367</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535135685736</v>
+        <v>148.8535448461689</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9110108259473</v>
+        <v>148.9249006635237</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.2909377918153</v>
+        <v>149.2952144033669</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4222888826206</v>
+        <v>150.4035767136539</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8997071144252</v>
+        <v>151.850585608772</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.2911016993117</v>
+        <v>152.2388586863635</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.6195428180878</v>
+        <v>152.5690781626131</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.2044583185796</v>
+        <v>153.1722827692848</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4154536189139</v>
+        <v>152.4074058769682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.9717005361675</v>
+        <v>152.8936852041283</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.7773633820941</v>
+        <v>152.6700221752745</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.8244402674729</v>
+        <v>152.6840344541098</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.5367349035052</v>
+        <v>154.3663312693258</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.4931109801591</v>
+        <v>155.3236028983225</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.4949691430095</v>
+        <v>156.309673756665</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>158.1649524869631</v>
+        <v>157.9616847021549</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.753014653285</v>
+        <v>159.5827120637965</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.544325825536</v>
+        <v>161.4331594504844</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.8509996382289</v>
+        <v>159.9157238041773</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.5968685477674</v>
+        <v>159.6290442249504</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.0527973330267</v>
+        <v>159.2491480083893</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.2561720963494</v>
+        <v>157.5108138303517</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>157.7929728086198</v>
+        <v>158.0366514815926</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.1226510472318</v>
+        <v>158.3465017885545</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.1718487259662</v>
+        <v>158.395510982474</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.4212238971686</v>
+        <v>159.6316882897088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.3602829147946</v>
+        <v>158.4511122127715</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7852732680265</v>
+        <v>155.7043463007535</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.9338904686024</v>
+        <v>155.8474783418609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6918133437926</v>
+        <v>156.6564765930944</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.4787707773145</v>
+        <v>156.2665625794468</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.2546490020273</v>
+        <v>156.0306838814209</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>156.1041252389548</v>
+        <v>155.8606031586961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.2820991629691</v>
+        <v>157.1375907618337</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6276921555173</v>
+        <v>158.6656587558901</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1050672996292</v>
+        <v>159.1654777961861</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.6802368506278</v>
+        <v>159.7622630630581</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.5448075817803</v>
+        <v>159.6101250286733</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.0292239094989</v>
+        <v>160.1858890146912</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>159.7773997240638</v>
+        <v>160.0421418734097</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.5290061383703</v>
+        <v>159.8139140074317</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>159.888741531569</v>
+        <v>160.2975236317981</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.0236498583409</v>
+        <v>160.9995672067813</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>160.1164085064736</v>
+        <v>161.4424540807675</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>159.9377942743288</v>
+        <v>161.4039360646607</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>159.644323225198</v>
+        <v>160.5255264589884</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>159.532234190653</v>
+        <v>160.1632130541334</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>159.7180001901735</v>
+        <v>160.0085081150648</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.855110981848</v>
+        <v>160.060931964292</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.8694464382091</v>
+        <v>160.0200575539926</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>161.2050550889949</v>
+        <v>159.3156575551678</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>162.6273803221112</v>
+        <v>159.2172329271776</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>157.4555303644058</v>
+        <v>159.1204689994327</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>157.5695863759555</v>
+        <v>159.0369854512836</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>157.9745918000207</v>
+        <v>158.9682917838034</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.2117088684738</v>
+        <v>158.677457087851</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.565631275755</v>
+        <v>158.3698430948543</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>159.1768060040584</v>
+        <v>158.3531908425542</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>159.7240471993246</v>
+        <v>158.1772622031864</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>160.4506580050188</v>
+        <v>158.6451988362532</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>161.0597756827065</v>
+        <v>158.6328010479529</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>161.6901158753492</v>
+        <v>158.8253857783249</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>162.3612655043751</v>
+        <v>157.8245482563085</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>162.9887903822166</v>
+        <v>157.3877368183942</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>163.4057437462531</v>
+        <v>159.3643841093397</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>163.5140564753324</v>
+        <v>161.3005231510286</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>165.1104287468766</v>
+        <v>163.732563918041</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>166.4625126393049</v>
+        <v>166.1038168461124</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>164.2153251393049</v>
+        <v>163.8566293461124</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>158.322</v>
+        <v>134.1368181818182</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>158.7680577940857</v>
+        <v>133.2338817141337</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>159.2940878711952</v>
+        <v>132.4801645834087</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>160.3311116137639</v>
+        <v>137.7524006697015</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>161.0738022194565</v>
+        <v>137.7223266666385</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>162.016419949635</v>
+        <v>138.5660795798738</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>162.8516208909859</v>
+        <v>138.1491509312019</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>163.6633291367978</v>
+        <v>140.1550164900376</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>164.3545136488576</v>
+        <v>141.1749861410947</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>165.5206209489425</v>
+        <v>139.2168822966655</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>166.3269349058928</v>
+        <v>137.2360488815717</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>167.0491757799211</v>
+        <v>137.7324375256904</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>167.4736458693121</v>
+        <v>139.5803657458182</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>139.7858901726152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>139.7449025504887</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>143.0863431043691</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>147.1651496517944</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>148.745226922968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>148.0383418429367</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>147.3111169743385</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>149.913999321388</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>150.3276923869192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>149.1457950138613</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>150.6637499528139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>153.3996598574483</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>156.7033551000668</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>157.0220445649639</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>147.2120379523794</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>152.0390014648438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>150.218994140625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>157.6439971923828</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>155.8272837853576</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>151.373992919922</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>148.632323063789</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>145.577</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>143.518</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>140.040885156207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>140.804378268202</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>141.253297461114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>141.288660994318</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>139.2956065462247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>142.4593993104129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>143.7372899031585</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>144.4151254981757</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>144.3412324279917</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>144.262681957354</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>144.2190090232445</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>144.2584595688052</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>144.928434152707</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>148.03722657516</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>148.4316237332169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>148.8535449960316</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>148.9250232892729</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>149.295254308169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>150.4034108255757</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>151.8501433866436</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>152.238387390752</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>152.5686205350662</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>153.1719904575597</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>152.4073343581107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>152.8929961231383</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>152.6690696419136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>152.6827779950231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>154.3648021206403</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>155.3220730191034</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>156.3079948043785</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>157.9598316507133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>159.5811321762869</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>161.4321097356958</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>159.9162477920906</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>159.6292863740798</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>159.2508678964255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>157.5130661716358</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>158.0388247299012</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>158.3485195853218</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>158.3975884143846</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>159.6336627500769</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>158.4520056022824</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>155.7036523003736</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>155.8467384985716</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>156.6562027801758</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>156.2646380402765</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>156.0286375623827</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>155.858341857223</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>157.1362385385345</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>158.6660187693344</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>159.1660549092541</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>159.7630499234799</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>159.6102827795196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>160.1861470904266</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>160.0416467206354</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>159.8129303144389</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>160.2966899058135</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>160.998313182511</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>161.4409001957096</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>161.4027384656596</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>160.5258522722123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>160.1640727220925</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>160.009797295623</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>160.0625811222075</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>160.0228843580713</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>159.3210803669347</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>159.2239268618949</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>159.1271976475905</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>159.0441222217633</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>158.9753084278163</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>158.6637344517217</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>158.3655566380865</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>158.3442052741964</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>158.1840777520265</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>158.651425392614</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>158.6509169797164</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>158.8506459146543</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>157.8974988148927</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>157.4910325014882</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>159.4103119538142</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>161.2469903975187</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>163.4628065214485</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>167.9235833903527</v>
+      <c r="B120">
+        <v>165.4063630353485</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>161.5951299389337</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDJPY_forecast.xlsx
+++ b/public/data/files/USDJPY_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>139.2956065462247</v>
+        <v>139.2949829391877</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>142.4593993104129</v>
+        <v>142.4584855237221</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>143.7372899031585</v>
+        <v>143.7362974508909</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>144.4151254981757</v>
+        <v>144.4141032846382</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>144.3412324279917</v>
+        <v>144.3401929906036</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>144.262681957354</v>
+        <v>144.2616280552844</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>144.2190090232445</v>
+        <v>144.2179494052516</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>144.2584595688052</v>
+        <v>144.257401857968</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>144.928434152707</v>
+        <v>144.9273707686952</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>148.03722657516</v>
+        <v>148.0372429033115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>148.4316237332169</v>
+        <v>148.4316272502937</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>148.8535449960316</v>
+        <v>148.8535451410078</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>148.9250232892729</v>
+        <v>148.9251437580537</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>149.295254308169</v>
+        <v>149.295293547816</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>150.4034108255757</v>
+        <v>150.4032478442001</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>151.8501433866436</v>
+        <v>151.8497087949938</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>152.238387390752</v>
+        <v>152.2379242106613</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>152.5686205350662</v>
+        <v>152.5681707474928</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>153.1719904575597</v>
+        <v>153.1717031437315</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>152.4073343581107</v>
+        <v>152.4072640887643</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>152.8929961231383</v>
+        <v>152.8923191609265</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>152.6690696419136</v>
+        <v>152.6681337875147</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>152.6827779950231</v>
+        <v>152.6815433530972</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>154.3648021206403</v>
+        <v>154.3632994534663</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>155.3220730191034</v>
+        <v>155.3205694889196</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>156.3079948043785</v>
+        <v>156.3063446610553</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>157.9598316507133</v>
+        <v>157.9580102099097</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>159.5811321762869</v>
+        <v>159.5795787850816</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>161.4321097356958</v>
+        <v>161.4310773037491</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>159.9162477920906</v>
+        <v>159.9167617235956</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>159.6292863740798</v>
+        <v>159.6295235255374</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>159.2508678964255</v>
+        <v>159.2525572635348</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>157.5130661716358</v>
+        <v>157.5152789244986</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>158.0388247299012</v>
+        <v>158.0409600765859</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>158.3485195853218</v>
+        <v>158.3505025469375</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>158.3975884143846</v>
+        <v>158.3996310699929</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>159.6336627500769</v>
+        <v>159.6356044851088</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>158.4520056022824</v>
+        <v>158.4528848686004</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>155.7036523003736</v>
+        <v>155.7029708750265</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>155.8467384985716</v>
+        <v>155.8460120869482</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>156.6562027801758</v>
+        <v>156.6559344668131</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>156.2646380402765</v>
+        <v>156.2627464934343</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>156.0286375623827</v>
+        <v>156.0266260709283</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>155.858341857223</v>
+        <v>155.8561184059974</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>157.1362385385345</v>
+        <v>157.1349087651544</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>158.6660187693344</v>
+        <v>158.666372881402</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>159.1660549092541</v>
+        <v>159.1666226361501</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>159.7630499234799</v>
+        <v>159.7638240354473</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>159.6102827795196</v>
+        <v>159.6104383129888</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>160.1861470904266</v>
+        <v>160.186401534187</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>160.0416467206354</v>
+        <v>160.0411605726489</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>159.8129303144389</v>
+        <v>159.8119636273709</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>160.2966899058135</v>
+        <v>160.295870623841</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>160.998313182511</v>
+        <v>160.9970805659945</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>161.4409001957096</v>
+        <v>161.4393727877185</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>161.4027384656596</v>
+        <v>161.4015600193691</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>160.5258522722123</v>
+        <v>160.5261692693342</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>160.1640727220925</v>
+        <v>160.1649148924322</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>160.009797295623</v>
+        <v>160.0110623930725</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>160.0625811222075</v>
+        <v>160.0642019167866</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>160.0228843580713</v>
+        <v>160.0256627127686</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>159.3210803669347</v>
+        <v>159.3264087172446</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>159.2239268618949</v>
+        <v>159.2305075409342</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>159.1271976475905</v>
+        <v>159.1338178551071</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>159.0441222217633</v>
+        <v>159.0511487158026</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>158.9753084278163</v>
+        <v>158.9822227000826</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>158.6637344517217</v>
+        <v>158.6533020851641</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>158.3655566380865</v>
+        <v>158.3642701051631</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>158.3442052741964</v>
+        <v>158.3382866686289</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>158.1840777520265</v>
+        <v>158.1896182511237</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>158.651425392614</v>
+        <v>158.6575631179021</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>158.6509169797164</v>
+        <v>158.6695585190249</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>158.8506459146543</v>
+        <v>158.8770427649283</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>157.8974988148927</v>
+        <v>157.9693583885874</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>157.4910325014882</v>
+        <v>157.591122318505</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>159.4103119538142</v>
+        <v>159.4563274522039</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>161.2469903975187</v>
+        <v>161.2032930171977</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>163.4628065214485</v>
+        <v>163.2357237668405</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>165.4063630353485</v>
+        <v>164.8669538322657</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>161.5951299389337</v>
+        <v>161.5440117571183</v>
       </c>
     </row>
   </sheetData>
